--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Box\Yolo_Food_Web\Data\tabular\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kristinn\Downloads\wq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2622D096-9AA3-4E21-AE39-D55F2AE30330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082080F-BB4F-465A-96D5-4BA32ABAC219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="66">
   <si>
     <t>RowID</t>
   </si>
@@ -553,14 +553,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y130"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Y144"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="10.54296875" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -637,7 +637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -708,7 +708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -776,7 +776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -847,7 +847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6799,14 +6799,14 @@
         <v>160074</v>
       </c>
       <c r="U90">
-        <f t="shared" ref="U90:U130" si="7">T90-S90</f>
+        <f t="shared" ref="U90:U143" si="7">T90-S90</f>
         <v>633</v>
       </c>
       <c r="V90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9377,7 +9377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -9586,6 +9586,968 @@
         <v>602</v>
       </c>
       <c r="V130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>45</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="E131">
+        <v>9.85</v>
+      </c>
+      <c r="F131">
+        <v>91.3</v>
+      </c>
+      <c r="G131">
+        <v>10.32</v>
+      </c>
+      <c r="H131">
+        <v>736</v>
+      </c>
+      <c r="I131">
+        <v>478.584</v>
+      </c>
+      <c r="J131">
+        <v>0.36</v>
+      </c>
+      <c r="K131">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="L131">
+        <v>32.93</v>
+      </c>
+      <c r="M131">
+        <v>1.39</v>
+      </c>
+      <c r="N131">
+        <v>38.619999999999997</v>
+      </c>
+      <c r="O131">
+        <v>31.51</v>
+      </c>
+      <c r="P131">
+        <v>3.5</v>
+      </c>
+      <c r="Q131">
+        <v>30</v>
+      </c>
+      <c r="R131">
+        <v>4</v>
+      </c>
+      <c r="S131">
+        <v>12842</v>
+      </c>
+      <c r="T131">
+        <v>13501</v>
+      </c>
+      <c r="U131">
+        <f t="shared" si="7"/>
+        <v>659</v>
+      </c>
+      <c r="V131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0.39374999999999999</v>
+      </c>
+      <c r="E132">
+        <v>9.8130000000000006</v>
+      </c>
+      <c r="F132">
+        <v>92.4</v>
+      </c>
+      <c r="G132">
+        <v>10.48</v>
+      </c>
+      <c r="H132">
+        <v>167.9</v>
+      </c>
+      <c r="I132">
+        <v>109.167</v>
+      </c>
+      <c r="J132">
+        <v>0.08</v>
+      </c>
+      <c r="K132">
+        <v>7.89</v>
+      </c>
+      <c r="L132">
+        <v>12.86</v>
+      </c>
+      <c r="M132">
+        <v>0.21</v>
+      </c>
+      <c r="N132">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="O132">
+        <v>16.73</v>
+      </c>
+      <c r="P132">
+        <v>2</v>
+      </c>
+      <c r="Q132">
+        <v>30</v>
+      </c>
+      <c r="R132">
+        <v>4</v>
+      </c>
+      <c r="S132">
+        <v>13501</v>
+      </c>
+      <c r="T132">
+        <v>14135</v>
+      </c>
+      <c r="U132">
+        <f t="shared" si="7"/>
+        <v>634</v>
+      </c>
+      <c r="V132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>29</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0.40625</v>
+      </c>
+      <c r="E133">
+        <v>10.066000000000001</v>
+      </c>
+      <c r="F133">
+        <v>94</v>
+      </c>
+      <c r="G133">
+        <v>10.58</v>
+      </c>
+      <c r="H133">
+        <v>322.10000000000002</v>
+      </c>
+      <c r="I133">
+        <v>209.36799999999999</v>
+      </c>
+      <c r="J133">
+        <v>0.15</v>
+      </c>
+      <c r="K133">
+        <v>7.8</v>
+      </c>
+      <c r="L133">
+        <v>9.26</v>
+      </c>
+      <c r="M133">
+        <v>0.67</v>
+      </c>
+      <c r="N133">
+        <v>10.46</v>
+      </c>
+      <c r="O133">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="P133">
+        <v>1.5</v>
+      </c>
+      <c r="Q133">
+        <v>30</v>
+      </c>
+      <c r="R133">
+        <v>4</v>
+      </c>
+      <c r="S133">
+        <v>14135</v>
+      </c>
+      <c r="T133">
+        <v>14793</v>
+      </c>
+      <c r="U133">
+        <f t="shared" si="7"/>
+        <v>658</v>
+      </c>
+      <c r="V133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="E134">
+        <v>9.9670000000000005</v>
+      </c>
+      <c r="F134">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="G134">
+        <v>7.82</v>
+      </c>
+      <c r="H134">
+        <v>596</v>
+      </c>
+      <c r="I134">
+        <v>387.47800000000001</v>
+      </c>
+      <c r="J134">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K134">
+        <v>7.81</v>
+      </c>
+      <c r="L134">
+        <v>25.61</v>
+      </c>
+      <c r="M134">
+        <v>0.59</v>
+      </c>
+      <c r="N134">
+        <v>7.37</v>
+      </c>
+      <c r="O134">
+        <v>76.28</v>
+      </c>
+      <c r="P134">
+        <v>4.5</v>
+      </c>
+      <c r="Q134">
+        <v>30</v>
+      </c>
+      <c r="R134">
+        <v>4</v>
+      </c>
+      <c r="S134">
+        <v>14793</v>
+      </c>
+      <c r="T134">
+        <v>15583</v>
+      </c>
+      <c r="U134">
+        <f t="shared" si="7"/>
+        <v>790</v>
+      </c>
+      <c r="V134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C135" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0.45555555555555555</v>
+      </c>
+      <c r="E135">
+        <v>10.141999999999999</v>
+      </c>
+      <c r="F135">
+        <v>108.1</v>
+      </c>
+      <c r="G135">
+        <v>12.15</v>
+      </c>
+      <c r="H135">
+        <v>552</v>
+      </c>
+      <c r="I135">
+        <v>358.88799999999998</v>
+      </c>
+      <c r="J135">
+        <v>0.27</v>
+      </c>
+      <c r="K135">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="L135">
+        <v>14.85</v>
+      </c>
+      <c r="M135">
+        <v>0.73</v>
+      </c>
+      <c r="N135">
+        <v>11.81</v>
+      </c>
+      <c r="O135">
+        <v>71.61</v>
+      </c>
+      <c r="P135">
+        <v>3.5</v>
+      </c>
+      <c r="Q135">
+        <v>30</v>
+      </c>
+      <c r="R135">
+        <v>4</v>
+      </c>
+      <c r="S135">
+        <v>15595</v>
+      </c>
+      <c r="T135">
+        <v>16275</v>
+      </c>
+      <c r="U135">
+        <f t="shared" si="7"/>
+        <v>680</v>
+      </c>
+      <c r="V135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>56</v>
+      </c>
+      <c r="C136" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0.47430555555555554</v>
+      </c>
+      <c r="E136">
+        <v>10.645</v>
+      </c>
+      <c r="F136">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="G136">
+        <v>8.66</v>
+      </c>
+      <c r="H136">
+        <v>203</v>
+      </c>
+      <c r="I136">
+        <v>132.268</v>
+      </c>
+      <c r="J136">
+        <v>0.1</v>
+      </c>
+      <c r="K136">
+        <v>7.65</v>
+      </c>
+      <c r="L136">
+        <v>12.03</v>
+      </c>
+      <c r="M136">
+        <v>0.39</v>
+      </c>
+      <c r="N136">
+        <v>4.46</v>
+      </c>
+      <c r="O136">
+        <v>35.06</v>
+      </c>
+      <c r="P136">
+        <v>5</v>
+      </c>
+      <c r="Q136">
+        <v>30</v>
+      </c>
+      <c r="R136">
+        <v>4</v>
+      </c>
+      <c r="S136">
+        <v>16279</v>
+      </c>
+      <c r="T136">
+        <v>16929</v>
+      </c>
+      <c r="U136">
+        <f t="shared" si="7"/>
+        <v>650</v>
+      </c>
+      <c r="V136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="E137">
+        <v>10.531000000000001</v>
+      </c>
+      <c r="F137">
+        <v>79</v>
+      </c>
+      <c r="G137">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="H137">
+        <v>547</v>
+      </c>
+      <c r="I137">
+        <v>355.83100000000002</v>
+      </c>
+      <c r="J137">
+        <v>0.27</v>
+      </c>
+      <c r="K137">
+        <v>7.89</v>
+      </c>
+      <c r="L137">
+        <v>22.32</v>
+      </c>
+      <c r="M137">
+        <v>0.72</v>
+      </c>
+      <c r="N137">
+        <v>13.97</v>
+      </c>
+      <c r="O137">
+        <v>70.540000000000006</v>
+      </c>
+      <c r="P137">
+        <v>4</v>
+      </c>
+      <c r="Q137">
+        <v>30</v>
+      </c>
+      <c r="R137">
+        <v>4</v>
+      </c>
+      <c r="S137">
+        <v>17527</v>
+      </c>
+      <c r="T137">
+        <v>18105</v>
+      </c>
+      <c r="U137">
+        <f t="shared" si="7"/>
+        <v>578</v>
+      </c>
+      <c r="V137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>32</v>
+      </c>
+      <c r="C138" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="E138">
+        <v>10.215999999999999</v>
+      </c>
+      <c r="F138">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G138">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H138">
+        <v>529</v>
+      </c>
+      <c r="I138">
+        <v>344.15</v>
+      </c>
+      <c r="J138">
+        <v>0.26</v>
+      </c>
+      <c r="K138">
+        <v>7.89</v>
+      </c>
+      <c r="L138">
+        <v>21.45</v>
+      </c>
+      <c r="M138">
+        <v>0.73</v>
+      </c>
+      <c r="N138">
+        <v>15.08</v>
+      </c>
+      <c r="O138">
+        <v>71.5</v>
+      </c>
+      <c r="P138">
+        <v>4.5</v>
+      </c>
+      <c r="Q138">
+        <v>30</v>
+      </c>
+      <c r="R138">
+        <v>4</v>
+      </c>
+      <c r="S138">
+        <v>18105</v>
+      </c>
+      <c r="T138">
+        <v>18830</v>
+      </c>
+      <c r="U138">
+        <f t="shared" si="7"/>
+        <v>725</v>
+      </c>
+      <c r="V138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>33</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="E139">
+        <v>10.455</v>
+      </c>
+      <c r="F139">
+        <v>78.7</v>
+      </c>
+      <c r="G139">
+        <v>8.77</v>
+      </c>
+      <c r="H139">
+        <v>519</v>
+      </c>
+      <c r="I139">
+        <v>337.15699999999998</v>
+      </c>
+      <c r="J139">
+        <v>0.25</v>
+      </c>
+      <c r="K139">
+        <v>7.85</v>
+      </c>
+      <c r="L139">
+        <v>21.25</v>
+      </c>
+      <c r="M139">
+        <v>0.7</v>
+      </c>
+      <c r="N139">
+        <v>13.62</v>
+      </c>
+      <c r="O139">
+        <v>73.94</v>
+      </c>
+      <c r="P139">
+        <v>4.5</v>
+      </c>
+      <c r="Q139">
+        <v>30</v>
+      </c>
+      <c r="R139">
+        <v>4</v>
+      </c>
+      <c r="S139">
+        <v>18888</v>
+      </c>
+      <c r="T139">
+        <v>19502</v>
+      </c>
+      <c r="U139">
+        <f t="shared" si="7"/>
+        <v>614</v>
+      </c>
+      <c r="V139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>41</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0.39444444444444443</v>
+      </c>
+      <c r="E140">
+        <v>7.9669999999999996</v>
+      </c>
+      <c r="F140">
+        <v>65.3</v>
+      </c>
+      <c r="G140">
+        <v>7.73</v>
+      </c>
+      <c r="H140">
+        <v>501</v>
+      </c>
+      <c r="I140">
+        <v>325.86</v>
+      </c>
+      <c r="J140">
+        <v>0.24</v>
+      </c>
+      <c r="K140">
+        <v>7.63</v>
+      </c>
+      <c r="L140">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="M140">
+        <v>0.19</v>
+      </c>
+      <c r="N140">
+        <v>2.09</v>
+      </c>
+      <c r="O140">
+        <v>77.02</v>
+      </c>
+      <c r="P140">
+        <v>5</v>
+      </c>
+      <c r="Q140">
+        <v>15</v>
+      </c>
+      <c r="R140">
+        <v>4</v>
+      </c>
+      <c r="S140" t="s">
+        <v>24</v>
+      </c>
+      <c r="T140" t="s">
+        <v>24</v>
+      </c>
+      <c r="U140" t="s">
+        <v>24</v>
+      </c>
+      <c r="V140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>42</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="E141">
+        <v>9.9480000000000004</v>
+      </c>
+      <c r="F141">
+        <v>62.1</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141">
+        <v>586</v>
+      </c>
+      <c r="I141">
+        <v>380.60300000000001</v>
+      </c>
+      <c r="J141">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K141">
+        <v>7.68</v>
+      </c>
+      <c r="L141">
+        <v>20.83</v>
+      </c>
+      <c r="M141">
+        <v>0.44</v>
+      </c>
+      <c r="N141">
+        <v>7.1</v>
+      </c>
+      <c r="O141">
+        <v>78.3</v>
+      </c>
+      <c r="P141" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>24</v>
+      </c>
+      <c r="R141" t="s">
+        <v>24</v>
+      </c>
+      <c r="S141" t="s">
+        <v>24</v>
+      </c>
+      <c r="T141" t="s">
+        <v>24</v>
+      </c>
+      <c r="U141" t="s">
+        <v>24</v>
+      </c>
+      <c r="V141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>61</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0.44027777777777777</v>
+      </c>
+      <c r="E142">
+        <v>9.0920000000000005</v>
+      </c>
+      <c r="F142">
+        <v>96.4</v>
+      </c>
+      <c r="G142">
+        <v>11.11</v>
+      </c>
+      <c r="H142">
+        <v>304.89999999999998</v>
+      </c>
+      <c r="I142">
+        <v>198.154</v>
+      </c>
+      <c r="J142">
+        <v>0.15</v>
+      </c>
+      <c r="K142">
+        <v>7.82</v>
+      </c>
+      <c r="L142">
+        <v>57.66</v>
+      </c>
+      <c r="M142">
+        <v>0.6</v>
+      </c>
+      <c r="N142">
+        <v>15.26</v>
+      </c>
+      <c r="O142">
+        <v>41.66</v>
+      </c>
+      <c r="P142">
+        <v>4</v>
+      </c>
+      <c r="Q142">
+        <v>15</v>
+      </c>
+      <c r="R142" t="s">
+        <v>24</v>
+      </c>
+      <c r="S142" t="s">
+        <v>24</v>
+      </c>
+      <c r="T142" t="s">
+        <v>24</v>
+      </c>
+      <c r="U142" t="s">
+        <v>24</v>
+      </c>
+      <c r="V142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>34</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E143">
+        <v>11.422000000000001</v>
+      </c>
+      <c r="F143">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="G143">
+        <v>7.35</v>
+      </c>
+      <c r="H143">
+        <v>417.2</v>
+      </c>
+      <c r="I143">
+        <v>271.19799999999998</v>
+      </c>
+      <c r="J143">
+        <v>0.2</v>
+      </c>
+      <c r="K143">
+        <v>7.42</v>
+      </c>
+      <c r="L143">
+        <v>4.58</v>
+      </c>
+      <c r="M143">
+        <v>0.25</v>
+      </c>
+      <c r="N143">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="O143">
+        <v>88.42</v>
+      </c>
+      <c r="P143">
+        <v>5</v>
+      </c>
+      <c r="Q143">
+        <v>30</v>
+      </c>
+      <c r="R143">
+        <v>4</v>
+      </c>
+      <c r="S143">
+        <v>8835</v>
+      </c>
+      <c r="T143">
+        <v>9472</v>
+      </c>
+      <c r="U143">
+        <f t="shared" si="7"/>
+        <v>637</v>
+      </c>
+      <c r="V143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>36</v>
+      </c>
+      <c r="C144" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="E144">
+        <v>14.577999999999999</v>
+      </c>
+      <c r="F144">
+        <v>54.8</v>
+      </c>
+      <c r="G144">
+        <v>5.58</v>
+      </c>
+      <c r="H144">
+        <v>359.4</v>
+      </c>
+      <c r="I144">
+        <v>233.63200000000001</v>
+      </c>
+      <c r="J144">
+        <v>0.17</v>
+      </c>
+      <c r="K144">
+        <v>7.25</v>
+      </c>
+      <c r="L144">
+        <v>20.260000000000002</v>
+      </c>
+      <c r="M144">
+        <v>0.11</v>
+      </c>
+      <c r="N144">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="O144">
+        <v>58.41</v>
+      </c>
+      <c r="P144">
+        <v>5</v>
+      </c>
+      <c r="Q144">
+        <v>15</v>
+      </c>
+      <c r="R144">
+        <v>4</v>
+      </c>
+      <c r="S144" t="s">
+        <v>24</v>
+      </c>
+      <c r="T144" t="s">
+        <v>24</v>
+      </c>
+      <c r="U144" t="s">
+        <v>24</v>
+      </c>
+      <c r="V144">
         <v>1</v>
       </c>
     </row>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kristinn\Downloads\wq\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kristinn\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082080F-BB4F-465A-96D5-4BA32ABAC219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{DF4F414E-7754-416B-A942-8B6CCBBB419D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="67">
   <si>
     <t>RowID</t>
   </si>
@@ -235,15 +235,24 @@
   <si>
     <t>Flow meter rotations suspect</t>
   </si>
+  <si>
+    <t>Missing cod end on net</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -553,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y144"/>
+  <dimension ref="A1:Y158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -6799,7 +6808,7 @@
         <v>160074</v>
       </c>
       <c r="U90">
-        <f t="shared" ref="U90:U143" si="7">T90-S90</f>
+        <f t="shared" ref="U90:U153" si="7">T90-S90</f>
         <v>633</v>
       </c>
       <c r="V90">
@@ -10398,8 +10407,8 @@
       <c r="Q142">
         <v>15</v>
       </c>
-      <c r="R142" t="s">
-        <v>24</v>
+      <c r="R142">
+        <v>4</v>
       </c>
       <c r="S142" t="s">
         <v>24</v>
@@ -10551,7 +10560,973 @@
         <v>1</v>
       </c>
     </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>45</v>
+      </c>
+      <c r="C145" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0.34513888888888888</v>
+      </c>
+      <c r="E145">
+        <v>11.208</v>
+      </c>
+      <c r="F145">
+        <v>90.5</v>
+      </c>
+      <c r="G145">
+        <v>9.9</v>
+      </c>
+      <c r="H145">
+        <v>873</v>
+      </c>
+      <c r="I145">
+        <v>567.64200000000005</v>
+      </c>
+      <c r="J145">
+        <v>0.43</v>
+      </c>
+      <c r="K145">
+        <v>8.27</v>
+      </c>
+      <c r="L145">
+        <v>16.25</v>
+      </c>
+      <c r="M145">
+        <v>0.38</v>
+      </c>
+      <c r="N145">
+        <v>14.2</v>
+      </c>
+      <c r="O145">
+        <v>24.33</v>
+      </c>
+      <c r="P145">
+        <v>3.5</v>
+      </c>
+      <c r="Q145">
+        <v>30</v>
+      </c>
+      <c r="R145">
+        <v>4</v>
+      </c>
+      <c r="S145">
+        <v>175305</v>
+      </c>
+      <c r="T145">
+        <v>175968</v>
+      </c>
+      <c r="U145">
+        <f t="shared" si="7"/>
+        <v>663</v>
+      </c>
+      <c r="V145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C146" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0.37430555555555556</v>
+      </c>
+      <c r="E146">
+        <v>10.978999999999999</v>
+      </c>
+      <c r="F146">
+        <v>98.1</v>
+      </c>
+      <c r="G146">
+        <v>10.82</v>
+      </c>
+      <c r="H146">
+        <v>170.3</v>
+      </c>
+      <c r="I146">
+        <v>110.70699999999999</v>
+      </c>
+      <c r="J146">
+        <v>0.08</v>
+      </c>
+      <c r="K146">
+        <v>7.83</v>
+      </c>
+      <c r="L146">
+        <v>11.62</v>
+      </c>
+      <c r="M146">
+        <v>0.2</v>
+      </c>
+      <c r="N146">
+        <v>2.13</v>
+      </c>
+      <c r="O146">
+        <v>13.9</v>
+      </c>
+      <c r="P146">
+        <v>2</v>
+      </c>
+      <c r="Q146">
+        <v>30</v>
+      </c>
+      <c r="R146">
+        <v>4</v>
+      </c>
+      <c r="S146">
+        <v>175968</v>
+      </c>
+      <c r="T146">
+        <v>176612</v>
+      </c>
+      <c r="U146">
+        <f t="shared" si="7"/>
+        <v>644</v>
+      </c>
+      <c r="V146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>29</v>
+      </c>
+      <c r="C147" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0.39513888888888887</v>
+      </c>
+      <c r="E147">
+        <v>10.8</v>
+      </c>
+      <c r="F147">
+        <v>94.7</v>
+      </c>
+      <c r="G147">
+        <v>10.49</v>
+      </c>
+      <c r="H147">
+        <v>170</v>
+      </c>
+      <c r="I147">
+        <v>110.511</v>
+      </c>
+      <c r="J147">
+        <v>0.08</v>
+      </c>
+      <c r="K147">
+        <v>7.7</v>
+      </c>
+      <c r="L147">
+        <v>11.47</v>
+      </c>
+      <c r="M147">
+        <v>0.11</v>
+      </c>
+      <c r="N147">
+        <v>2.04</v>
+      </c>
+      <c r="O147">
+        <v>14.12</v>
+      </c>
+      <c r="P147">
+        <v>1.5</v>
+      </c>
+      <c r="Q147">
+        <v>30</v>
+      </c>
+      <c r="R147">
+        <v>4</v>
+      </c>
+      <c r="S147">
+        <v>176612</v>
+      </c>
+      <c r="T147">
+        <v>177218</v>
+      </c>
+      <c r="U147">
+        <f t="shared" si="7"/>
+        <v>606</v>
+      </c>
+      <c r="V147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0.41944444444444445</v>
+      </c>
+      <c r="E148">
+        <v>11.53</v>
+      </c>
+      <c r="F148">
+        <v>77.7</v>
+      </c>
+      <c r="G148">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="H148">
+        <v>565</v>
+      </c>
+      <c r="I148">
+        <v>367.40300000000002</v>
+      </c>
+      <c r="J148">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K148">
+        <v>7.82</v>
+      </c>
+      <c r="L148">
+        <v>23.18</v>
+      </c>
+      <c r="M148">
+        <v>0.3</v>
+      </c>
+      <c r="N148">
+        <v>5.79</v>
+      </c>
+      <c r="O148">
+        <v>61.2</v>
+      </c>
+      <c r="P148">
+        <v>3</v>
+      </c>
+      <c r="Q148">
+        <v>30</v>
+      </c>
+      <c r="R148">
+        <v>4</v>
+      </c>
+      <c r="S148">
+        <v>177218</v>
+      </c>
+      <c r="T148">
+        <v>177785</v>
+      </c>
+      <c r="U148">
+        <f t="shared" si="7"/>
+        <v>567</v>
+      </c>
+      <c r="V148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0.44513888888888886</v>
+      </c>
+      <c r="E149">
+        <v>12.92</v>
+      </c>
+      <c r="F149">
+        <v>114.7</v>
+      </c>
+      <c r="G149">
+        <v>12.09</v>
+      </c>
+      <c r="H149">
+        <v>620</v>
+      </c>
+      <c r="I149">
+        <v>402.85700000000003</v>
+      </c>
+      <c r="J149">
+        <v>0.3</v>
+      </c>
+      <c r="K149">
+        <v>8.67</v>
+      </c>
+      <c r="L149">
+        <v>10.67</v>
+      </c>
+      <c r="M149">
+        <v>0.35</v>
+      </c>
+      <c r="N149">
+        <v>9.11</v>
+      </c>
+      <c r="O149">
+        <v>62.49</v>
+      </c>
+      <c r="P149">
+        <v>5</v>
+      </c>
+      <c r="Q149">
+        <v>30</v>
+      </c>
+      <c r="R149">
+        <v>4</v>
+      </c>
+      <c r="S149">
+        <v>177785</v>
+      </c>
+      <c r="T149">
+        <v>178424</v>
+      </c>
+      <c r="U149">
+        <f t="shared" si="7"/>
+        <v>639</v>
+      </c>
+      <c r="V149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>56</v>
+      </c>
+      <c r="C150" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0.46736111111111112</v>
+      </c>
+      <c r="E150">
+        <v>13.569000000000001</v>
+      </c>
+      <c r="F150">
+        <v>90</v>
+      </c>
+      <c r="G150">
+        <v>9.35</v>
+      </c>
+      <c r="H150">
+        <v>504</v>
+      </c>
+      <c r="I150">
+        <v>327.57299999999998</v>
+      </c>
+      <c r="J150">
+        <v>0.24</v>
+      </c>
+      <c r="K150">
+        <v>8.1</v>
+      </c>
+      <c r="L150">
+        <v>78.16</v>
+      </c>
+      <c r="M150">
+        <v>1.29</v>
+      </c>
+      <c r="N150">
+        <v>25.99</v>
+      </c>
+      <c r="O150">
+        <v>30.71</v>
+      </c>
+      <c r="P150">
+        <v>5</v>
+      </c>
+      <c r="Q150">
+        <v>30</v>
+      </c>
+      <c r="R150">
+        <v>4</v>
+      </c>
+      <c r="S150">
+        <v>178424</v>
+      </c>
+      <c r="T150">
+        <v>179033</v>
+      </c>
+      <c r="U150">
+        <f t="shared" si="7"/>
+        <v>609</v>
+      </c>
+      <c r="V150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>31</v>
+      </c>
+      <c r="C151" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="E151">
+        <v>12.526</v>
+      </c>
+      <c r="F151">
+        <v>77</v>
+      </c>
+      <c r="G151">
+        <v>8.18</v>
+      </c>
+      <c r="H151">
+        <v>567</v>
+      </c>
+      <c r="I151">
+        <v>368.50900000000001</v>
+      </c>
+      <c r="J151">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K151">
+        <v>7.84</v>
+      </c>
+      <c r="L151">
+        <v>22.64</v>
+      </c>
+      <c r="M151">
+        <v>0.3</v>
+      </c>
+      <c r="N151">
+        <v>7.58</v>
+      </c>
+      <c r="O151">
+        <v>58.77</v>
+      </c>
+      <c r="P151">
+        <v>3.5</v>
+      </c>
+      <c r="Q151">
+        <v>30</v>
+      </c>
+      <c r="R151">
+        <v>4</v>
+      </c>
+      <c r="S151">
+        <v>179033</v>
+      </c>
+      <c r="T151">
+        <v>179659</v>
+      </c>
+      <c r="U151">
+        <f t="shared" si="7"/>
+        <v>626</v>
+      </c>
+      <c r="V151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>32</v>
+      </c>
+      <c r="C152" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="E152">
+        <v>12.545999999999999</v>
+      </c>
+      <c r="F152">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="G152">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="H152">
+        <v>578</v>
+      </c>
+      <c r="I152">
+        <v>375.541</v>
+      </c>
+      <c r="J152">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K152">
+        <v>7.82</v>
+      </c>
+      <c r="L152">
+        <v>22.1</v>
+      </c>
+      <c r="M152">
+        <v>0.35</v>
+      </c>
+      <c r="N152">
+        <v>9.1</v>
+      </c>
+      <c r="O152">
+        <v>60.21</v>
+      </c>
+      <c r="P152">
+        <v>3.5</v>
+      </c>
+      <c r="Q152">
+        <v>30</v>
+      </c>
+      <c r="R152">
+        <v>4</v>
+      </c>
+      <c r="S152">
+        <v>179659</v>
+      </c>
+      <c r="T152">
+        <v>180265</v>
+      </c>
+      <c r="U152">
+        <f t="shared" si="7"/>
+        <v>606</v>
+      </c>
+      <c r="V152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>33</v>
+      </c>
+      <c r="C153" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D153" s="2">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="E153">
+        <v>12.407999999999999</v>
+      </c>
+      <c r="F153">
+        <v>77</v>
+      </c>
+      <c r="G153">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="H153">
+        <v>575</v>
+      </c>
+      <c r="I153">
+        <v>373.70499999999998</v>
+      </c>
+      <c r="J153">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K153">
+        <v>7.8</v>
+      </c>
+      <c r="L153">
+        <v>18.16</v>
+      </c>
+      <c r="M153">
+        <v>0.4</v>
+      </c>
+      <c r="N153">
+        <v>8.65</v>
+      </c>
+      <c r="O153">
+        <v>58.95</v>
+      </c>
+      <c r="P153">
+        <v>4</v>
+      </c>
+      <c r="Q153">
+        <v>30</v>
+      </c>
+      <c r="R153">
+        <v>4</v>
+      </c>
+      <c r="S153">
+        <v>180265</v>
+      </c>
+      <c r="T153">
+        <v>180858</v>
+      </c>
+      <c r="U153">
+        <f t="shared" si="7"/>
+        <v>593</v>
+      </c>
+      <c r="V153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D154" s="2">
+        <v>0.36527777777777776</v>
+      </c>
+      <c r="E154">
+        <v>11.74</v>
+      </c>
+      <c r="F154">
+        <v>44</v>
+      </c>
+      <c r="G154">
+        <v>4.76</v>
+      </c>
+      <c r="H154">
+        <v>537</v>
+      </c>
+      <c r="I154">
+        <v>348.80399999999997</v>
+      </c>
+      <c r="J154">
+        <v>0.26</v>
+      </c>
+      <c r="K154">
+        <v>7.47</v>
+      </c>
+      <c r="L154">
+        <v>5.03</v>
+      </c>
+      <c r="M154">
+        <v>0.2</v>
+      </c>
+      <c r="N154">
+        <v>1.73</v>
+      </c>
+      <c r="O154">
+        <v>82.7</v>
+      </c>
+      <c r="P154" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>24</v>
+      </c>
+      <c r="R154" t="s">
+        <v>24</v>
+      </c>
+      <c r="S154" t="s">
+        <v>24</v>
+      </c>
+      <c r="T154" t="s">
+        <v>24</v>
+      </c>
+      <c r="U154" t="s">
+        <v>24</v>
+      </c>
+      <c r="V154">
+        <v>1</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>41</v>
+      </c>
+      <c r="C155" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D155" s="2">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="E155">
+        <v>12.023</v>
+      </c>
+      <c r="F155">
+        <v>46.1</v>
+      </c>
+      <c r="G155">
+        <v>4.96</v>
+      </c>
+      <c r="H155">
+        <v>539</v>
+      </c>
+      <c r="I155">
+        <v>350.10599999999999</v>
+      </c>
+      <c r="J155">
+        <v>0.26</v>
+      </c>
+      <c r="K155">
+        <v>7.5</v>
+      </c>
+      <c r="L155">
+        <v>7.44</v>
+      </c>
+      <c r="M155">
+        <v>0.16</v>
+      </c>
+      <c r="N155">
+        <v>1.84</v>
+      </c>
+      <c r="O155">
+        <v>81.06</v>
+      </c>
+      <c r="P155">
+        <v>4.5</v>
+      </c>
+      <c r="Q155">
+        <v>30</v>
+      </c>
+      <c r="R155">
+        <v>4</v>
+      </c>
+      <c r="S155">
+        <v>9955</v>
+      </c>
+      <c r="T155">
+        <v>10535</v>
+      </c>
+      <c r="U155">
+        <f t="shared" ref="U154:U158" si="8">T155-S155</f>
+        <v>580</v>
+      </c>
+      <c r="V155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>42</v>
+      </c>
+      <c r="C156" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D156" s="2">
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="E156">
+        <v>12.367000000000001</v>
+      </c>
+      <c r="F156">
+        <v>81.7</v>
+      </c>
+      <c r="G156">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="H156">
+        <v>648</v>
+      </c>
+      <c r="I156">
+        <v>421.36500000000001</v>
+      </c>
+      <c r="J156">
+        <v>0.32</v>
+      </c>
+      <c r="K156">
+        <v>7.93</v>
+      </c>
+      <c r="L156">
+        <v>20.39</v>
+      </c>
+      <c r="M156">
+        <v>0.38</v>
+      </c>
+      <c r="N156">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O156">
+        <v>81.96</v>
+      </c>
+      <c r="P156" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>24</v>
+      </c>
+      <c r="R156" t="s">
+        <v>24</v>
+      </c>
+      <c r="S156" t="s">
+        <v>24</v>
+      </c>
+      <c r="T156" t="s">
+        <v>24</v>
+      </c>
+      <c r="U156" t="s">
+        <v>24</v>
+      </c>
+      <c r="V156" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>61</v>
+      </c>
+      <c r="C157" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D157" s="2">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="E157">
+        <v>12.903</v>
+      </c>
+      <c r="F157">
+        <v>98.1</v>
+      </c>
+      <c r="G157">
+        <v>10.35</v>
+      </c>
+      <c r="H157">
+        <v>374.2</v>
+      </c>
+      <c r="I157">
+        <v>243.21199999999999</v>
+      </c>
+      <c r="J157">
+        <v>0.18</v>
+      </c>
+      <c r="K157">
+        <v>7.73</v>
+      </c>
+      <c r="L157">
+        <v>78.28</v>
+      </c>
+      <c r="M157">
+        <v>0.99</v>
+      </c>
+      <c r="N157">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="O157">
+        <v>45.8</v>
+      </c>
+      <c r="P157">
+        <v>4.5</v>
+      </c>
+      <c r="Q157">
+        <v>15</v>
+      </c>
+      <c r="R157">
+        <v>4</v>
+      </c>
+      <c r="S157" t="s">
+        <v>24</v>
+      </c>
+      <c r="T157" t="s">
+        <v>24</v>
+      </c>
+      <c r="U157" t="s">
+        <v>24</v>
+      </c>
+      <c r="V157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>34</v>
+      </c>
+      <c r="C158" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D158" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E158">
+        <v>14.545</v>
+      </c>
+      <c r="F158">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="G158">
+        <v>7.79</v>
+      </c>
+      <c r="H158">
+        <v>549</v>
+      </c>
+      <c r="I158">
+        <v>357.14499999999998</v>
+      </c>
+      <c r="J158">
+        <v>0.27</v>
+      </c>
+      <c r="K158">
+        <v>7.43</v>
+      </c>
+      <c r="L158">
+        <v>5.17</v>
+      </c>
+      <c r="M158">
+        <v>0.22</v>
+      </c>
+      <c r="N158">
+        <v>2.9</v>
+      </c>
+      <c r="O158">
+        <v>89.15</v>
+      </c>
+      <c r="P158">
+        <v>5</v>
+      </c>
+      <c r="Q158">
+        <v>15</v>
+      </c>
+      <c r="R158">
+        <v>4</v>
+      </c>
+      <c r="S158" t="s">
+        <v>24</v>
+      </c>
+      <c r="T158" t="s">
+        <v>24</v>
+      </c>
+      <c r="U158" t="s">
+        <v>24</v>
+      </c>
+      <c r="V158">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Box\Yolo_Food_Web\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="13_ncr:1_{3AFD425C-1797-475E-8EFF-D332B24BA87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE017823-1393-460C-872D-4976FEACD737}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416E154-FDFB-4B9B-878A-86C1F8869F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -267,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,13 +600,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z210"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="24" max="25" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="24" max="25" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -760,7 +760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -831,7 +831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -905,7 +905,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:26">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:26">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="1:26">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:26">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:26">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:26">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:26">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:26">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:26">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:26">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:26">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:26">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:26">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:26">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:26">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:26">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:26">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:26">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:26">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:26">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:26">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:26">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:26">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:26">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:26">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:26">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:26">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:26">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:26">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:26">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:26">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:26">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:26">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:26">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:26">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:26">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8561,7 +8561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:26">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:26">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:26">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:26">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="117" spans="1:26">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:26">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:26">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:26">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:26">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:26">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:26">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:26">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:26">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:26">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:26">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:26">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10520,7 +10520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -11017,7 +11017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:26">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:26">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:26">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11230,7 +11230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:26">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11301,7 +11301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:26">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:26">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:26">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:26">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:26">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:26">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11727,7 +11727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:26">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:26">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:26">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:26">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:26">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -12085,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:26">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:23">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:23">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:23" s="3" customFormat="1">
+    <row r="164" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:23">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:23">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:23">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -12656,7 +12656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:23">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:23">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:23">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:23">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:23">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:23">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:23">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:23">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:23">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:23">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:23">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:23">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:23">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:23">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:23">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -13730,7 +13730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:23">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:23">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:23">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:23">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:23">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:23">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -14661,78 +14661,78 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:23">
-      <c r="A196">
+    <row r="196" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="3">
         <v>195</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D196" s="1">
+      <c r="D196" s="4">
         <v>46076</v>
       </c>
-      <c r="E196" s="2">
+      <c r="E196" s="5">
         <v>0.47083333333333333</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="3">
         <v>14.978</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="3">
         <v>111.6</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="3">
         <v>11.24</v>
       </c>
-      <c r="I196">
+      <c r="I196" s="3">
         <v>556</v>
       </c>
-      <c r="J196">
+      <c r="J196" s="3">
         <v>366.351</v>
       </c>
-      <c r="K196">
+      <c r="K196" s="3">
         <v>0.27</v>
       </c>
-      <c r="L196">
+      <c r="L196" s="3">
         <v>8.15</v>
       </c>
-      <c r="M196">
+      <c r="M196" s="3">
         <v>14.79</v>
       </c>
-      <c r="N196">
+      <c r="N196" s="3">
         <v>0.6</v>
       </c>
-      <c r="O196">
+      <c r="O196" s="3">
         <v>17.420000000000002</v>
       </c>
-      <c r="P196">
+      <c r="P196" s="3">
         <v>62.25</v>
       </c>
-      <c r="Q196" t="s">
-        <v>28</v>
-      </c>
-      <c r="R196" t="s">
-        <v>28</v>
-      </c>
-      <c r="S196" t="s">
-        <v>28</v>
-      </c>
-      <c r="T196" t="s">
-        <v>28</v>
-      </c>
-      <c r="U196" t="s">
-        <v>28</v>
-      </c>
-      <c r="V196" t="s">
-        <v>28</v>
-      </c>
-      <c r="W196" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="197" spans="1:23">
+      <c r="Q196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="S196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W196" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -14804,7 +14804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:23">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:23">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -15164,7 +15164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:23">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:23">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -15380,7 +15380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:23">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="15">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:23">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -15594,7 +15594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:23">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15665,7 +15665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:23">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.35">
       <c r="D210" s="1"/>
     </row>
   </sheetData>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Box\Yolo_Food_Web\Data\tabular\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Documents\R\Projects\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416E154-FDFB-4B9B-878A-86C1F8869F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766FA540-7C25-4A10-B0EB-1D3A0FFF5659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="75">
   <si>
     <t>RowID</t>
   </si>
@@ -599,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z210"/>
+  <dimension ref="A1:Z222"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12.453125" customWidth="1"/>
@@ -12090,7 +12090,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C160" t="s">
         <v>39</v>
@@ -15666,7 +15666,927 @@
       </c>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="D210" s="1"/>
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>31</v>
+      </c>
+      <c r="C210" t="s">
+        <v>58</v>
+      </c>
+      <c r="D210" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E210" s="2">
+        <v>0.34513888888888888</v>
+      </c>
+      <c r="F210">
+        <v>15.343999999999999</v>
+      </c>
+      <c r="G210">
+        <v>100.4</v>
+      </c>
+      <c r="H210">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="I210">
+        <v>470.3</v>
+      </c>
+      <c r="J210">
+        <v>305.72199999999998</v>
+      </c>
+      <c r="K210">
+        <v>0.23</v>
+      </c>
+      <c r="L210">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="M210">
+        <v>14.49</v>
+      </c>
+      <c r="N210">
+        <v>0.75</v>
+      </c>
+      <c r="O210">
+        <v>37.5</v>
+      </c>
+      <c r="P210">
+        <v>31.86</v>
+      </c>
+      <c r="Q210">
+        <v>3.5</v>
+      </c>
+      <c r="R210">
+        <v>30</v>
+      </c>
+      <c r="S210">
+        <v>4</v>
+      </c>
+      <c r="T210">
+        <v>23902</v>
+      </c>
+      <c r="U210">
+        <v>24435</v>
+      </c>
+      <c r="V210">
+        <v>533</v>
+      </c>
+      <c r="W210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>31</v>
+      </c>
+      <c r="C211" t="s">
+        <v>32</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E211" s="2">
+        <v>0.37638888888888888</v>
+      </c>
+      <c r="F211">
+        <v>13.526999999999999</v>
+      </c>
+      <c r="G211">
+        <v>90.1</v>
+      </c>
+      <c r="H211">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="I211">
+        <v>165.7</v>
+      </c>
+      <c r="J211">
+        <v>107.726</v>
+      </c>
+      <c r="K211">
+        <v>0.08</v>
+      </c>
+      <c r="L211">
+        <v>7.65</v>
+      </c>
+      <c r="M211">
+        <v>63.61</v>
+      </c>
+      <c r="N211">
+        <v>0.17</v>
+      </c>
+      <c r="O211">
+        <v>0.93</v>
+      </c>
+      <c r="P211">
+        <v>20.5</v>
+      </c>
+      <c r="Q211">
+        <v>1.5</v>
+      </c>
+      <c r="R211">
+        <v>30</v>
+      </c>
+      <c r="S211">
+        <v>4</v>
+      </c>
+      <c r="T211">
+        <v>24435</v>
+      </c>
+      <c r="U211">
+        <v>25126</v>
+      </c>
+      <c r="V211">
+        <v>691</v>
+      </c>
+      <c r="W211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>31</v>
+      </c>
+      <c r="C212" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E212" s="2">
+        <v>0.39374999999999999</v>
+      </c>
+      <c r="F212">
+        <v>13.683999999999999</v>
+      </c>
+      <c r="G212">
+        <v>94.2</v>
+      </c>
+      <c r="H212">
+        <v>9.77</v>
+      </c>
+      <c r="I212">
+        <v>168.8</v>
+      </c>
+      <c r="J212">
+        <v>109.714</v>
+      </c>
+      <c r="K212">
+        <v>0.08</v>
+      </c>
+      <c r="L212">
+        <v>7.72</v>
+      </c>
+      <c r="M212">
+        <v>64.209999999999994</v>
+      </c>
+      <c r="N212">
+        <v>0.19</v>
+      </c>
+      <c r="O212">
+        <v>0.84</v>
+      </c>
+      <c r="P212">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="Q212">
+        <v>1.5</v>
+      </c>
+      <c r="R212">
+        <v>30</v>
+      </c>
+      <c r="S212">
+        <v>4</v>
+      </c>
+      <c r="T212">
+        <v>25132</v>
+      </c>
+      <c r="U212">
+        <v>25739</v>
+      </c>
+      <c r="V212">
+        <v>607</v>
+      </c>
+      <c r="W212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>31</v>
+      </c>
+      <c r="C213" t="s">
+        <v>35</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E213" s="2">
+        <v>0.41458333333333336</v>
+      </c>
+      <c r="F213">
+        <v>14.507</v>
+      </c>
+      <c r="G213">
+        <v>82.1</v>
+      </c>
+      <c r="H213">
+        <v>8.36</v>
+      </c>
+      <c r="I213">
+        <v>318.89999999999998</v>
+      </c>
+      <c r="J213">
+        <v>207.29900000000001</v>
+      </c>
+      <c r="K213">
+        <v>0.15</v>
+      </c>
+      <c r="L213">
+        <v>7.7</v>
+      </c>
+      <c r="M213">
+        <v>46.93</v>
+      </c>
+      <c r="N213">
+        <v>0.21</v>
+      </c>
+      <c r="O213">
+        <v>4.58</v>
+      </c>
+      <c r="P213">
+        <v>42.54</v>
+      </c>
+      <c r="Q213">
+        <v>3.5</v>
+      </c>
+      <c r="R213">
+        <v>30</v>
+      </c>
+      <c r="S213">
+        <v>4</v>
+      </c>
+      <c r="T213">
+        <v>25739</v>
+      </c>
+      <c r="U213">
+        <v>26280</v>
+      </c>
+      <c r="V213">
+        <v>541</v>
+      </c>
+      <c r="W213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>31</v>
+      </c>
+      <c r="C214" t="s">
+        <v>51</v>
+      </c>
+      <c r="D214" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E214" s="2">
+        <v>0.43541666666666667</v>
+      </c>
+      <c r="F214">
+        <v>15.423999999999999</v>
+      </c>
+      <c r="G214">
+        <v>91.9</v>
+      </c>
+      <c r="H214">
+        <v>9.18</v>
+      </c>
+      <c r="I214">
+        <v>273.60000000000002</v>
+      </c>
+      <c r="J214">
+        <v>177.83500000000001</v>
+      </c>
+      <c r="K214">
+        <v>0.13</v>
+      </c>
+      <c r="L214">
+        <v>7.83</v>
+      </c>
+      <c r="M214">
+        <v>53.78</v>
+      </c>
+      <c r="N214">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O214">
+        <v>5.45</v>
+      </c>
+      <c r="P214">
+        <v>36.270000000000003</v>
+      </c>
+      <c r="Q214">
+        <v>3.5</v>
+      </c>
+      <c r="R214">
+        <v>30</v>
+      </c>
+      <c r="S214">
+        <v>4</v>
+      </c>
+      <c r="T214">
+        <v>26280</v>
+      </c>
+      <c r="U214">
+        <v>26819</v>
+      </c>
+      <c r="V214">
+        <v>539</v>
+      </c>
+      <c r="W214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>31</v>
+      </c>
+      <c r="C215" t="s">
+        <v>53</v>
+      </c>
+      <c r="D215" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E215" s="2">
+        <v>0.44861111111111113</v>
+      </c>
+      <c r="F215">
+        <v>17.457999999999998</v>
+      </c>
+      <c r="G215">
+        <v>91.6</v>
+      </c>
+      <c r="H215">
+        <v>8.76</v>
+      </c>
+      <c r="I215">
+        <v>439.6</v>
+      </c>
+      <c r="J215">
+        <v>285.74299999999999</v>
+      </c>
+      <c r="K215">
+        <v>0.21</v>
+      </c>
+      <c r="L215">
+        <v>8.02</v>
+      </c>
+      <c r="M215">
+        <v>21.28</v>
+      </c>
+      <c r="N215">
+        <v>0.37</v>
+      </c>
+      <c r="O215">
+        <v>11.95</v>
+      </c>
+      <c r="P215">
+        <v>50.86</v>
+      </c>
+      <c r="Q215">
+        <v>5</v>
+      </c>
+      <c r="R215">
+        <v>30</v>
+      </c>
+      <c r="S215">
+        <v>4</v>
+      </c>
+      <c r="T215">
+        <v>26819</v>
+      </c>
+      <c r="U215">
+        <v>27447</v>
+      </c>
+      <c r="V215">
+        <v>628</v>
+      </c>
+      <c r="W215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>31</v>
+      </c>
+      <c r="C216" t="s">
+        <v>36</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E216" s="2">
+        <v>0.48125000000000001</v>
+      </c>
+      <c r="F216">
+        <v>15.848000000000001</v>
+      </c>
+      <c r="G216">
+        <v>83.8</v>
+      </c>
+      <c r="H216">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="I216">
+        <v>231.2</v>
+      </c>
+      <c r="J216">
+        <v>150.202</v>
+      </c>
+      <c r="K216">
+        <v>0.11</v>
+      </c>
+      <c r="L216">
+        <v>7.63</v>
+      </c>
+      <c r="M216">
+        <v>55.28</v>
+      </c>
+      <c r="N216">
+        <v>0.27</v>
+      </c>
+      <c r="O216">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="P216">
+        <v>34.04</v>
+      </c>
+      <c r="Q216">
+        <v>3</v>
+      </c>
+      <c r="R216">
+        <v>30</v>
+      </c>
+      <c r="S216">
+        <v>4</v>
+      </c>
+      <c r="T216">
+        <v>27452</v>
+      </c>
+      <c r="U216">
+        <v>27972</v>
+      </c>
+      <c r="V216">
+        <v>520</v>
+      </c>
+      <c r="W216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>31</v>
+      </c>
+      <c r="C217" t="s">
+        <v>38</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E217" s="2">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="F217">
+        <v>16.094999999999999</v>
+      </c>
+      <c r="G217">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="H217">
+        <v>6.93</v>
+      </c>
+      <c r="I217">
+        <v>195.5</v>
+      </c>
+      <c r="J217">
+        <v>127.04600000000001</v>
+      </c>
+      <c r="K217">
+        <v>0.09</v>
+      </c>
+      <c r="L217">
+        <v>7.4</v>
+      </c>
+      <c r="M217">
+        <v>56.13</v>
+      </c>
+      <c r="N217">
+        <v>0.33</v>
+      </c>
+      <c r="O217">
+        <v>9.08</v>
+      </c>
+      <c r="P217">
+        <v>38.6</v>
+      </c>
+      <c r="Q217">
+        <v>4</v>
+      </c>
+      <c r="R217">
+        <v>30</v>
+      </c>
+      <c r="S217">
+        <v>4</v>
+      </c>
+      <c r="T217">
+        <v>27982</v>
+      </c>
+      <c r="U217">
+        <v>28559</v>
+      </c>
+      <c r="V217">
+        <v>577</v>
+      </c>
+      <c r="W217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>31</v>
+      </c>
+      <c r="C218" t="s">
+        <v>37</v>
+      </c>
+      <c r="D218" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E218" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F218">
+        <v>15.819000000000001</v>
+      </c>
+      <c r="G218">
+        <v>80.2</v>
+      </c>
+      <c r="H218">
+        <v>7.94</v>
+      </c>
+      <c r="I218">
+        <v>196.9</v>
+      </c>
+      <c r="J218">
+        <v>127.965</v>
+      </c>
+      <c r="K218">
+        <v>0.09</v>
+      </c>
+      <c r="L218">
+        <v>7.55</v>
+      </c>
+      <c r="M218">
+        <v>62.47</v>
+      </c>
+      <c r="N218">
+        <v>0.4</v>
+      </c>
+      <c r="O218">
+        <v>3.54</v>
+      </c>
+      <c r="P218">
+        <v>32.42</v>
+      </c>
+      <c r="Q218">
+        <v>3</v>
+      </c>
+      <c r="R218">
+        <v>30</v>
+      </c>
+      <c r="S218">
+        <v>4</v>
+      </c>
+      <c r="T218">
+        <v>28559</v>
+      </c>
+      <c r="U218">
+        <v>29242</v>
+      </c>
+      <c r="V218">
+        <v>683</v>
+      </c>
+      <c r="W218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>31</v>
+      </c>
+      <c r="C219" t="s">
+        <v>46</v>
+      </c>
+      <c r="D219" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E219" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F219">
+        <v>17.224</v>
+      </c>
+      <c r="G219">
+        <v>63.2</v>
+      </c>
+      <c r="H219">
+        <v>6.07</v>
+      </c>
+      <c r="I219">
+        <v>610</v>
+      </c>
+      <c r="J219">
+        <v>396.488</v>
+      </c>
+      <c r="K219">
+        <v>0.3</v>
+      </c>
+      <c r="L219">
+        <v>7.72</v>
+      </c>
+      <c r="M219">
+        <v>17.25</v>
+      </c>
+      <c r="N219">
+        <v>0.48</v>
+      </c>
+      <c r="O219">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="P219">
+        <v>87.32</v>
+      </c>
+      <c r="Q219">
+        <v>2.5</v>
+      </c>
+      <c r="R219">
+        <v>30</v>
+      </c>
+      <c r="S219">
+        <v>4</v>
+      </c>
+      <c r="T219">
+        <v>18720</v>
+      </c>
+      <c r="U219">
+        <v>19301</v>
+      </c>
+      <c r="V219">
+        <v>581</v>
+      </c>
+      <c r="W219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>31</v>
+      </c>
+      <c r="C220" t="s">
+        <v>48</v>
+      </c>
+      <c r="D220" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E220" s="2">
+        <v>0.40069444444444446</v>
+      </c>
+      <c r="F220">
+        <v>17.338999999999999</v>
+      </c>
+      <c r="G220">
+        <v>71.5</v>
+      </c>
+      <c r="H220">
+        <v>6.85</v>
+      </c>
+      <c r="I220">
+        <v>604</v>
+      </c>
+      <c r="J220">
+        <v>392.87700000000001</v>
+      </c>
+      <c r="K220">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L220">
+        <v>7.75</v>
+      </c>
+      <c r="M220">
+        <v>16.27</v>
+      </c>
+      <c r="N220">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O220">
+        <v>10.1</v>
+      </c>
+      <c r="P220">
+        <v>88.94</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>28</v>
+      </c>
+      <c r="R220" t="s">
+        <v>28</v>
+      </c>
+      <c r="S220" t="s">
+        <v>28</v>
+      </c>
+      <c r="T220" t="s">
+        <v>28</v>
+      </c>
+      <c r="U220" t="s">
+        <v>28</v>
+      </c>
+      <c r="V220" t="s">
+        <v>28</v>
+      </c>
+      <c r="W220" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>31</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E221" s="2">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F221">
+        <v>16.568999999999999</v>
+      </c>
+      <c r="G221">
+        <v>91.8</v>
+      </c>
+      <c r="H221">
+        <v>8.94</v>
+      </c>
+      <c r="I221">
+        <v>481.4</v>
+      </c>
+      <c r="J221">
+        <v>312.92200000000003</v>
+      </c>
+      <c r="K221">
+        <v>0.23</v>
+      </c>
+      <c r="L221">
+        <v>7.66</v>
+      </c>
+      <c r="M221">
+        <v>50.06</v>
+      </c>
+      <c r="N221">
+        <v>1.23</v>
+      </c>
+      <c r="O221">
+        <v>31.81</v>
+      </c>
+      <c r="P221">
+        <v>74.87</v>
+      </c>
+      <c r="Q221">
+        <v>5</v>
+      </c>
+      <c r="R221">
+        <v>15</v>
+      </c>
+      <c r="S221">
+        <v>4</v>
+      </c>
+      <c r="T221" t="s">
+        <v>28</v>
+      </c>
+      <c r="U221" t="s">
+        <v>28</v>
+      </c>
+      <c r="V221" t="s">
+        <v>28</v>
+      </c>
+      <c r="W221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>31</v>
+      </c>
+      <c r="C222" t="s">
+        <v>39</v>
+      </c>
+      <c r="D222" s="1">
+        <v>46084</v>
+      </c>
+      <c r="E222" s="2">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="F222">
+        <v>16.492999999999999</v>
+      </c>
+      <c r="G222">
+        <v>69.5</v>
+      </c>
+      <c r="H222">
+        <v>6.78</v>
+      </c>
+      <c r="I222">
+        <v>198.5</v>
+      </c>
+      <c r="J222">
+        <v>129.00299999999999</v>
+      </c>
+      <c r="K222">
+        <v>0.09</v>
+      </c>
+      <c r="L222">
+        <v>7.36</v>
+      </c>
+      <c r="M222">
+        <v>46.61</v>
+      </c>
+      <c r="N222">
+        <v>0.51</v>
+      </c>
+      <c r="O222">
+        <v>6.81</v>
+      </c>
+      <c r="P222">
+        <v>39.81</v>
+      </c>
+      <c r="Q222">
+        <v>3.5</v>
+      </c>
+      <c r="R222">
+        <v>30</v>
+      </c>
+      <c r="S222">
+        <v>4</v>
+      </c>
+      <c r="T222">
+        <v>19311</v>
+      </c>
+      <c r="U222">
+        <v>19703</v>
+      </c>
+      <c r="V222">
+        <v>392</v>
+      </c>
+      <c r="W222">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Documents\R\Projects\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766FA540-7C25-4A10-B0EB-1D3A0FFF5659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE532961-F33C-46D5-B05E-F8045CE104A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="76">
   <si>
     <t>RowID</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>TC1</t>
+  </si>
+  <si>
+    <t>Adult midge sample for isotopes</t>
   </si>
 </sst>
 </file>
@@ -599,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z222"/>
+  <dimension ref="A1:Z235"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12.453125" customWidth="1"/>
@@ -15594,7 +15597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15665,7 +15668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -15736,7 +15739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -15807,7 +15810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -15878,7 +15881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -15949,7 +15952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -16020,7 +16023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -16091,7 +16094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -16162,7 +16165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -16233,7 +16236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -16304,7 +16307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -16375,7 +16378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -16446,7 +16449,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -16517,75 +16520,1028 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A222">
+    <row r="222" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="3">
         <v>221</v>
       </c>
-      <c r="B222" t="s">
-        <v>31</v>
-      </c>
-      <c r="C222" t="s">
+      <c r="B222" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D222" s="1">
+      <c r="D222" s="4">
         <v>46084</v>
       </c>
-      <c r="E222" s="2">
+      <c r="E222" s="5">
         <v>0.52222222222222225</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="3">
         <v>16.492999999999999</v>
       </c>
-      <c r="G222">
+      <c r="G222" s="3">
         <v>69.5</v>
       </c>
-      <c r="H222">
+      <c r="H222" s="3">
         <v>6.78</v>
       </c>
-      <c r="I222">
+      <c r="I222" s="3">
         <v>198.5</v>
       </c>
-      <c r="J222">
+      <c r="J222" s="3">
         <v>129.00299999999999</v>
       </c>
-      <c r="K222">
+      <c r="K222" s="3">
         <v>0.09</v>
       </c>
-      <c r="L222">
+      <c r="L222" s="3">
         <v>7.36</v>
       </c>
-      <c r="M222">
+      <c r="M222" s="3">
         <v>46.61</v>
       </c>
-      <c r="N222">
+      <c r="N222" s="3">
         <v>0.51</v>
       </c>
-      <c r="O222">
+      <c r="O222" s="3">
         <v>6.81</v>
       </c>
-      <c r="P222">
+      <c r="P222" s="3">
         <v>39.81</v>
       </c>
-      <c r="Q222">
+      <c r="Q222" s="3">
         <v>3.5</v>
       </c>
-      <c r="R222">
+      <c r="R222" s="3">
         <v>30</v>
       </c>
-      <c r="S222">
-        <v>4</v>
-      </c>
-      <c r="T222">
+      <c r="S222" s="3">
+        <v>4</v>
+      </c>
+      <c r="T222" s="3">
         <v>19311</v>
       </c>
-      <c r="U222">
+      <c r="U222" s="3">
         <v>19703</v>
       </c>
-      <c r="V222">
+      <c r="V222" s="3">
         <v>392</v>
       </c>
-      <c r="W222">
-        <v>1</v>
+      <c r="W222" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>31</v>
+      </c>
+      <c r="C223" t="s">
+        <v>32</v>
+      </c>
+      <c r="D223" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E223" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="F223">
+        <v>13.867000000000001</v>
+      </c>
+      <c r="G223">
+        <v>91.9</v>
+      </c>
+      <c r="H223">
+        <v>9.5</v>
+      </c>
+      <c r="I223">
+        <v>189.6</v>
+      </c>
+      <c r="J223">
+        <v>123.252</v>
+      </c>
+      <c r="K223">
+        <v>0.09</v>
+      </c>
+      <c r="L223">
+        <v>7.6</v>
+      </c>
+      <c r="M223">
+        <v>15.99</v>
+      </c>
+      <c r="N223">
+        <v>0.17</v>
+      </c>
+      <c r="O223">
+        <v>0.91</v>
+      </c>
+      <c r="P223">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="Q223">
+        <v>1.5</v>
+      </c>
+      <c r="R223">
+        <v>30</v>
+      </c>
+      <c r="S223">
+        <v>4</v>
+      </c>
+      <c r="T223">
+        <v>191883</v>
+      </c>
+      <c r="U223">
+        <v>192557</v>
+      </c>
+      <c r="V223">
+        <v>674</v>
+      </c>
+      <c r="W223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>31</v>
+      </c>
+      <c r="C224" t="s">
+        <v>34</v>
+      </c>
+      <c r="D224" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E224" s="2">
+        <v>0.34375</v>
+      </c>
+      <c r="F224">
+        <v>15.887</v>
+      </c>
+      <c r="G224">
+        <v>89.9</v>
+      </c>
+      <c r="H224">
+        <v>8.89</v>
+      </c>
+      <c r="I224">
+        <v>313.10000000000002</v>
+      </c>
+      <c r="J224">
+        <v>203.494</v>
+      </c>
+      <c r="K224">
+        <v>0.15</v>
+      </c>
+      <c r="L224">
+        <v>7.58</v>
+      </c>
+      <c r="M224">
+        <v>14.32</v>
+      </c>
+      <c r="N224">
+        <v>0.36</v>
+      </c>
+      <c r="O224">
+        <v>7.62</v>
+      </c>
+      <c r="P224">
+        <v>25.66</v>
+      </c>
+      <c r="Q224">
+        <v>1</v>
+      </c>
+      <c r="R224">
+        <v>30</v>
+      </c>
+      <c r="S224">
+        <v>4</v>
+      </c>
+      <c r="T224">
+        <v>192557</v>
+      </c>
+      <c r="U224">
+        <v>193161</v>
+      </c>
+      <c r="V224">
+        <v>604</v>
+      </c>
+      <c r="W224">
+        <v>1</v>
+      </c>
+      <c r="Z224" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="225" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>31</v>
+      </c>
+      <c r="C225" t="s">
+        <v>35</v>
+      </c>
+      <c r="D225" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E225" s="2">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="F225">
+        <v>15.641999999999999</v>
+      </c>
+      <c r="G225">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="H225">
+        <v>7.98</v>
+      </c>
+      <c r="I225">
+        <v>540</v>
+      </c>
+      <c r="J225">
+        <v>351.298</v>
+      </c>
+      <c r="K225">
+        <v>0.26</v>
+      </c>
+      <c r="L225">
+        <v>8.01</v>
+      </c>
+      <c r="M225">
+        <v>22.46</v>
+      </c>
+      <c r="N225">
+        <v>0.44</v>
+      </c>
+      <c r="O225">
+        <v>10.99</v>
+      </c>
+      <c r="P225">
+        <v>51.36</v>
+      </c>
+      <c r="Q225">
+        <v>4</v>
+      </c>
+      <c r="R225">
+        <v>30</v>
+      </c>
+      <c r="S225">
+        <v>4</v>
+      </c>
+      <c r="T225">
+        <v>193161</v>
+      </c>
+      <c r="U225">
+        <v>193768</v>
+      </c>
+      <c r="V225">
+        <v>607</v>
+      </c>
+      <c r="W225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>31</v>
+      </c>
+      <c r="C226" t="s">
+        <v>51</v>
+      </c>
+      <c r="D226" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E226" s="2">
+        <v>0.39027777777777778</v>
+      </c>
+      <c r="F226">
+        <v>16.777999999999999</v>
+      </c>
+      <c r="G226">
+        <v>110.9</v>
+      </c>
+      <c r="H226">
+        <v>10.76</v>
+      </c>
+      <c r="I226">
+        <v>521</v>
+      </c>
+      <c r="J226">
+        <v>338.64299999999997</v>
+      </c>
+      <c r="K226">
+        <v>0.25</v>
+      </c>
+      <c r="L226">
+        <v>8.77</v>
+      </c>
+      <c r="M226">
+        <v>18.73</v>
+      </c>
+      <c r="N226">
+        <v>0.53</v>
+      </c>
+      <c r="O226">
+        <v>15.36</v>
+      </c>
+      <c r="P226">
+        <v>43.9</v>
+      </c>
+      <c r="Q226">
+        <v>3</v>
+      </c>
+      <c r="R226">
+        <v>30</v>
+      </c>
+      <c r="S226">
+        <v>4</v>
+      </c>
+      <c r="T226">
+        <v>193768</v>
+      </c>
+      <c r="U226">
+        <v>194401</v>
+      </c>
+      <c r="V226">
+        <v>633</v>
+      </c>
+      <c r="W226">
+        <v>1</v>
+      </c>
+      <c r="Y226">
+        <v>1</v>
+      </c>
+      <c r="Z226" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="227" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>31</v>
+      </c>
+      <c r="C227" t="s">
+        <v>53</v>
+      </c>
+      <c r="D227" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E227" s="2">
+        <v>0.41180555555555554</v>
+      </c>
+      <c r="F227">
+        <v>17.074999999999999</v>
+      </c>
+      <c r="G227">
+        <v>77.5</v>
+      </c>
+      <c r="H227">
+        <v>7.47</v>
+      </c>
+      <c r="I227">
+        <v>274.5</v>
+      </c>
+      <c r="J227">
+        <v>178.43199999999999</v>
+      </c>
+      <c r="K227">
+        <v>0.13</v>
+      </c>
+      <c r="L227">
+        <v>7.73</v>
+      </c>
+      <c r="M227">
+        <v>10.55</v>
+      </c>
+      <c r="N227">
+        <v>0.15</v>
+      </c>
+      <c r="O227">
+        <v>2.14</v>
+      </c>
+      <c r="P227">
+        <v>37.43</v>
+      </c>
+      <c r="Q227">
+        <v>5</v>
+      </c>
+      <c r="R227">
+        <v>30</v>
+      </c>
+      <c r="S227">
+        <v>4</v>
+      </c>
+      <c r="T227">
+        <v>197185</v>
+      </c>
+      <c r="U227">
+        <v>197821</v>
+      </c>
+      <c r="V227">
+        <v>636</v>
+      </c>
+      <c r="W227">
+        <v>1</v>
+      </c>
+      <c r="Y227">
+        <v>1</v>
+      </c>
+      <c r="Z227" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="228" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>31</v>
+      </c>
+      <c r="C228" t="s">
+        <v>38</v>
+      </c>
+      <c r="D228" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E228" s="2">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="F228">
+        <v>17.274000000000001</v>
+      </c>
+      <c r="G228">
+        <v>87.1</v>
+      </c>
+      <c r="H228">
+        <v>8.36</v>
+      </c>
+      <c r="I228">
+        <v>498.5</v>
+      </c>
+      <c r="J228">
+        <v>324.03899999999999</v>
+      </c>
+      <c r="K228">
+        <v>0.24</v>
+      </c>
+      <c r="L228">
+        <v>8.08</v>
+      </c>
+      <c r="M228">
+        <v>20.78</v>
+      </c>
+      <c r="N228">
+        <v>0.63</v>
+      </c>
+      <c r="O228">
+        <v>16.71</v>
+      </c>
+      <c r="P228">
+        <v>49.85</v>
+      </c>
+      <c r="Q228">
+        <v>4</v>
+      </c>
+      <c r="R228">
+        <v>30</v>
+      </c>
+      <c r="S228">
+        <v>4</v>
+      </c>
+      <c r="T228">
+        <v>198554</v>
+      </c>
+      <c r="U228">
+        <v>199113</v>
+      </c>
+      <c r="V228">
+        <v>559</v>
+      </c>
+      <c r="W228">
+        <v>1</v>
+      </c>
+      <c r="Y228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>31</v>
+      </c>
+      <c r="C229" t="s">
+        <v>48</v>
+      </c>
+      <c r="D229" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E229" s="2">
+        <v>0.35972222222222222</v>
+      </c>
+      <c r="F229">
+        <v>15.471</v>
+      </c>
+      <c r="G229">
+        <v>57.4</v>
+      </c>
+      <c r="H229">
+        <v>5.72</v>
+      </c>
+      <c r="I229">
+        <v>754</v>
+      </c>
+      <c r="J229">
+        <v>490.16</v>
+      </c>
+      <c r="K229">
+        <v>0.37</v>
+      </c>
+      <c r="L229">
+        <v>7.83</v>
+      </c>
+      <c r="M229">
+        <v>18.18</v>
+      </c>
+      <c r="N229">
+        <v>0.26</v>
+      </c>
+      <c r="O229">
+        <v>7.77</v>
+      </c>
+      <c r="P229">
+        <v>88.19</v>
+      </c>
+      <c r="Q229">
+        <v>3</v>
+      </c>
+      <c r="R229">
+        <v>30</v>
+      </c>
+      <c r="S229">
+        <v>4</v>
+      </c>
+      <c r="T229">
+        <v>20376</v>
+      </c>
+      <c r="U229">
+        <v>21190</v>
+      </c>
+      <c r="V229">
+        <v>814</v>
+      </c>
+      <c r="W229">
+        <v>1</v>
+      </c>
+      <c r="Y229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>31</v>
+      </c>
+      <c r="C230" t="s">
+        <v>58</v>
+      </c>
+      <c r="D230" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E230" s="2">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="F230">
+        <v>14.946999999999999</v>
+      </c>
+      <c r="G230">
+        <v>97.8</v>
+      </c>
+      <c r="H230">
+        <v>9.86</v>
+      </c>
+      <c r="I230">
+        <v>338</v>
+      </c>
+      <c r="J230">
+        <v>251.88800000000001</v>
+      </c>
+      <c r="K230">
+        <v>0.19</v>
+      </c>
+      <c r="L230">
+        <v>8.32</v>
+      </c>
+      <c r="M230">
+        <v>24.51</v>
+      </c>
+      <c r="N230">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O230">
+        <v>24.14</v>
+      </c>
+      <c r="P230">
+        <v>23.27</v>
+      </c>
+      <c r="Q230">
+        <v>3</v>
+      </c>
+      <c r="R230">
+        <v>30</v>
+      </c>
+      <c r="S230">
+        <v>4</v>
+      </c>
+      <c r="T230">
+        <v>31798</v>
+      </c>
+      <c r="U230">
+        <v>32407</v>
+      </c>
+      <c r="V230">
+        <v>609</v>
+      </c>
+      <c r="W230">
+        <v>1</v>
+      </c>
+      <c r="Y230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>31</v>
+      </c>
+      <c r="C231" t="s">
+        <v>36</v>
+      </c>
+      <c r="D231" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E231" s="2">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="F231">
+        <v>17.731999999999999</v>
+      </c>
+      <c r="G231">
+        <v>98.6</v>
+      </c>
+      <c r="H231">
+        <v>9.36</v>
+      </c>
+      <c r="I231">
+        <v>511</v>
+      </c>
+      <c r="J231">
+        <v>332.12700000000001</v>
+      </c>
+      <c r="K231">
+        <v>0.25</v>
+      </c>
+      <c r="L231">
+        <v>8.27</v>
+      </c>
+      <c r="M231">
+        <v>19.86</v>
+      </c>
+      <c r="N231">
+        <v>0.52</v>
+      </c>
+      <c r="O231">
+        <v>21.46</v>
+      </c>
+      <c r="P231">
+        <v>46.66</v>
+      </c>
+      <c r="Q231">
+        <v>3.5</v>
+      </c>
+      <c r="R231">
+        <v>30</v>
+      </c>
+      <c r="S231">
+        <v>4</v>
+      </c>
+      <c r="T231">
+        <v>40962</v>
+      </c>
+      <c r="U231">
+        <v>41720</v>
+      </c>
+      <c r="V231">
+        <v>758</v>
+      </c>
+      <c r="W231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>31</v>
+      </c>
+      <c r="C232" t="s">
+        <v>37</v>
+      </c>
+      <c r="D232" s="1">
+        <v>46091</v>
+      </c>
+      <c r="E232" s="2">
+        <v>0.53125</v>
+      </c>
+      <c r="F232">
+        <v>17.268000000000001</v>
+      </c>
+      <c r="G232">
+        <v>91.2</v>
+      </c>
+      <c r="H232">
+        <v>8.75</v>
+      </c>
+      <c r="I232">
+        <v>504</v>
+      </c>
+      <c r="J232">
+        <v>327.51499999999999</v>
+      </c>
+      <c r="K232">
+        <v>0.24</v>
+      </c>
+      <c r="L232">
+        <v>8.18</v>
+      </c>
+      <c r="M232">
+        <v>22.3</v>
+      </c>
+      <c r="N232">
+        <v>0.51</v>
+      </c>
+      <c r="O232">
+        <v>21.17</v>
+      </c>
+      <c r="P232">
+        <v>47.64</v>
+      </c>
+      <c r="Q232">
+        <v>3.5</v>
+      </c>
+      <c r="R232">
+        <v>30</v>
+      </c>
+      <c r="S232">
+        <v>4</v>
+      </c>
+      <c r="T232">
+        <v>41717</v>
+      </c>
+      <c r="U232">
+        <v>42248</v>
+      </c>
+      <c r="V232">
+        <v>531</v>
+      </c>
+      <c r="W232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D233" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E233" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F233" s="3">
+        <v>19.126000000000001</v>
+      </c>
+      <c r="G233" s="3">
+        <v>88.4</v>
+      </c>
+      <c r="H233" s="3">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="I233" s="3">
+        <v>403.6</v>
+      </c>
+      <c r="J233" s="3">
+        <v>262.351</v>
+      </c>
+      <c r="K233" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="L233" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="M233" s="3">
+        <v>3.93</v>
+      </c>
+      <c r="N233" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="O233" s="3">
+        <v>5.04</v>
+      </c>
+      <c r="P233" s="3">
+        <v>64.09</v>
+      </c>
+      <c r="Q233" s="3">
+        <v>5</v>
+      </c>
+      <c r="R233" s="3">
+        <v>30</v>
+      </c>
+      <c r="S233" s="3">
+        <v>4</v>
+      </c>
+      <c r="T233" s="3">
+        <v>44289</v>
+      </c>
+      <c r="U233" s="3">
+        <v>44905</v>
+      </c>
+      <c r="V233" s="3">
+        <v>616</v>
+      </c>
+      <c r="W233" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y233" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z233" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="234" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>69</v>
+      </c>
+      <c r="C234" t="s">
+        <v>72</v>
+      </c>
+      <c r="D234" s="1">
+        <v>46092</v>
+      </c>
+      <c r="E234" s="2">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="F234">
+        <v>15.704000000000001</v>
+      </c>
+      <c r="G234">
+        <v>63.2</v>
+      </c>
+      <c r="H234">
+        <v>6.26</v>
+      </c>
+      <c r="I234">
+        <v>737</v>
+      </c>
+      <c r="J234">
+        <v>478.95699999999999</v>
+      </c>
+      <c r="K234">
+        <v>0.36</v>
+      </c>
+      <c r="L234">
+        <v>7.78</v>
+      </c>
+      <c r="M234">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="N234">
+        <v>0.32</v>
+      </c>
+      <c r="O234">
+        <v>6.36</v>
+      </c>
+      <c r="P234">
+        <v>81.84</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>28</v>
+      </c>
+      <c r="R234" t="s">
+        <v>28</v>
+      </c>
+      <c r="S234" t="s">
+        <v>28</v>
+      </c>
+      <c r="T234" t="s">
+        <v>28</v>
+      </c>
+      <c r="U234" t="s">
+        <v>28</v>
+      </c>
+      <c r="V234" t="s">
+        <v>28</v>
+      </c>
+      <c r="W234" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="235" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>69</v>
+      </c>
+      <c r="C235" t="s">
+        <v>58</v>
+      </c>
+      <c r="D235" s="1">
+        <v>46092</v>
+      </c>
+      <c r="E235" s="2">
+        <v>0.42083333333333334</v>
+      </c>
+      <c r="F235">
+        <v>13.952</v>
+      </c>
+      <c r="G235">
+        <v>99.1</v>
+      </c>
+      <c r="H235">
+        <v>99.1</v>
+      </c>
+      <c r="I235">
+        <v>385.5</v>
+      </c>
+      <c r="J235">
+        <v>250.55600000000001</v>
+      </c>
+      <c r="K235">
+        <v>0.19</v>
+      </c>
+      <c r="L235">
+        <v>8.24</v>
+      </c>
+      <c r="M235">
+        <v>28.29</v>
+      </c>
+      <c r="N235">
+        <v>0.78</v>
+      </c>
+      <c r="O235">
+        <v>18.34</v>
+      </c>
+      <c r="P235">
+        <v>22.46</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>28</v>
+      </c>
+      <c r="R235" t="s">
+        <v>28</v>
+      </c>
+      <c r="S235" t="s">
+        <v>28</v>
+      </c>
+      <c r="T235" t="s">
+        <v>28</v>
+      </c>
+      <c r="U235" t="s">
+        <v>28</v>
+      </c>
+      <c r="V235" t="s">
+        <v>28</v>
+      </c>
+      <c r="W235" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Documents\R\Projects\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE532961-F33C-46D5-B05E-F8045CE104A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED490F51-98E7-4318-A759-26B47CE2FB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="78">
   <si>
     <t>RowID</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>Adult midge sample for isotopes</t>
+  </si>
+  <si>
+    <t>Sampled in lower terrace</t>
+  </si>
+  <si>
+    <t>Sampled in EW fish passage channel</t>
   </si>
 </sst>
 </file>
@@ -602,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z235"/>
+  <dimension ref="A1:Z246"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12.453125" customWidth="1"/>
@@ -17544,6 +17550,793 @@
         <v>28</v>
       </c>
     </row>
+    <row r="236" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>31</v>
+      </c>
+      <c r="C236" t="s">
+        <v>32</v>
+      </c>
+      <c r="D236" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E236" s="2">
+        <v>0.3298611111111111</v>
+      </c>
+      <c r="F236">
+        <v>16.234000000000002</v>
+      </c>
+      <c r="G236">
+        <v>94.1</v>
+      </c>
+      <c r="H236">
+        <v>9.24</v>
+      </c>
+      <c r="I236">
+        <v>228.5</v>
+      </c>
+      <c r="J236">
+        <v>148.50800000000001</v>
+      </c>
+      <c r="K236">
+        <v>0.11</v>
+      </c>
+      <c r="L236">
+        <v>7.63</v>
+      </c>
+      <c r="M236">
+        <v>22.13</v>
+      </c>
+      <c r="N236">
+        <v>0.32</v>
+      </c>
+      <c r="O236">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="P236">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="Q236">
+        <v>2</v>
+      </c>
+      <c r="R236">
+        <v>30</v>
+      </c>
+      <c r="S236">
+        <v>4</v>
+      </c>
+      <c r="T236">
+        <v>199115</v>
+      </c>
+      <c r="U236">
+        <v>199606</v>
+      </c>
+      <c r="V236">
+        <v>491</v>
+      </c>
+      <c r="W236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>31</v>
+      </c>
+      <c r="C237" t="s">
+        <v>34</v>
+      </c>
+      <c r="D237" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E237" s="2">
+        <v>0.34583333333333333</v>
+      </c>
+      <c r="F237">
+        <v>18.959</v>
+      </c>
+      <c r="G237">
+        <v>83.4</v>
+      </c>
+      <c r="H237">
+        <v>7.73</v>
+      </c>
+      <c r="I237">
+        <v>498.6</v>
+      </c>
+      <c r="J237">
+        <v>324.10199999999998</v>
+      </c>
+      <c r="K237">
+        <v>0.24</v>
+      </c>
+      <c r="L237">
+        <v>7.7</v>
+      </c>
+      <c r="M237">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="N237">
+        <v>0.08</v>
+      </c>
+      <c r="O237">
+        <v>3.76</v>
+      </c>
+      <c r="P237">
+        <v>25.24</v>
+      </c>
+      <c r="Q237">
+        <v>1</v>
+      </c>
+      <c r="R237">
+        <v>30</v>
+      </c>
+      <c r="S237">
+        <v>4</v>
+      </c>
+      <c r="T237">
+        <v>199606</v>
+      </c>
+      <c r="U237">
+        <v>200052</v>
+      </c>
+      <c r="V237">
+        <v>446</v>
+      </c>
+      <c r="W237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>31</v>
+      </c>
+      <c r="C238" t="s">
+        <v>35</v>
+      </c>
+      <c r="D238" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E238" s="2">
+        <v>0.37083333333333335</v>
+      </c>
+      <c r="F238">
+        <v>18.885999999999999</v>
+      </c>
+      <c r="G238">
+        <v>81.5</v>
+      </c>
+      <c r="H238">
+        <v>7.56</v>
+      </c>
+      <c r="I238">
+        <v>579</v>
+      </c>
+      <c r="J238">
+        <v>376.113</v>
+      </c>
+      <c r="K238">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L238">
+        <v>7.94</v>
+      </c>
+      <c r="M238">
+        <v>20.99</v>
+      </c>
+      <c r="N238">
+        <v>0.15</v>
+      </c>
+      <c r="O238">
+        <v>5.95</v>
+      </c>
+      <c r="P238">
+        <v>36.93</v>
+      </c>
+      <c r="Q238">
+        <v>4.5</v>
+      </c>
+      <c r="R238">
+        <v>30</v>
+      </c>
+      <c r="S238">
+        <v>4</v>
+      </c>
+      <c r="T238">
+        <v>200052</v>
+      </c>
+      <c r="U238">
+        <v>200470</v>
+      </c>
+      <c r="V238">
+        <v>418</v>
+      </c>
+      <c r="W238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>31</v>
+      </c>
+      <c r="C239" t="s">
+        <v>51</v>
+      </c>
+      <c r="D239" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E239" s="2">
+        <v>0.39652777777777776</v>
+      </c>
+      <c r="F239">
+        <v>20.093</v>
+      </c>
+      <c r="G239">
+        <v>124.2</v>
+      </c>
+      <c r="H239">
+        <v>11.26</v>
+      </c>
+      <c r="I239">
+        <v>571</v>
+      </c>
+      <c r="J239">
+        <v>371.32600000000002</v>
+      </c>
+      <c r="K239">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L239">
+        <v>8.73</v>
+      </c>
+      <c r="M239">
+        <v>8.67</v>
+      </c>
+      <c r="N239">
+        <v>0.25</v>
+      </c>
+      <c r="O239">
+        <v>6.35</v>
+      </c>
+      <c r="P239">
+        <v>41.24</v>
+      </c>
+      <c r="Q239">
+        <v>1.5</v>
+      </c>
+      <c r="R239">
+        <v>15</v>
+      </c>
+      <c r="S239">
+        <v>4</v>
+      </c>
+      <c r="T239" t="s">
+        <v>28</v>
+      </c>
+      <c r="U239" t="s">
+        <v>28</v>
+      </c>
+      <c r="V239" t="s">
+        <v>28</v>
+      </c>
+      <c r="W239">
+        <v>1</v>
+      </c>
+      <c r="Z239" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="240" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>31</v>
+      </c>
+      <c r="C240" t="s">
+        <v>53</v>
+      </c>
+      <c r="D240" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E240" s="2">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="F240">
+        <v>21.870999999999999</v>
+      </c>
+      <c r="G240">
+        <v>82.2</v>
+      </c>
+      <c r="H240">
+        <v>7.2</v>
+      </c>
+      <c r="I240">
+        <v>323.3</v>
+      </c>
+      <c r="J240">
+        <v>210.12100000000001</v>
+      </c>
+      <c r="K240">
+        <v>0.15</v>
+      </c>
+      <c r="L240">
+        <v>7.89</v>
+      </c>
+      <c r="M240">
+        <v>32.619999999999997</v>
+      </c>
+      <c r="N240">
+        <v>0.33</v>
+      </c>
+      <c r="O240">
+        <v>5.91</v>
+      </c>
+      <c r="P240">
+        <v>33.03</v>
+      </c>
+      <c r="Q240">
+        <v>5</v>
+      </c>
+      <c r="R240">
+        <v>30</v>
+      </c>
+      <c r="S240">
+        <v>4</v>
+      </c>
+      <c r="T240">
+        <v>200700</v>
+      </c>
+      <c r="U240">
+        <v>201173</v>
+      </c>
+      <c r="V240">
+        <v>473</v>
+      </c>
+      <c r="W240">
+        <v>1</v>
+      </c>
+      <c r="Z240" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>31</v>
+      </c>
+      <c r="C241" t="s">
+        <v>48</v>
+      </c>
+      <c r="D241" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E241" s="2">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="F241">
+        <v>18.38</v>
+      </c>
+      <c r="G241">
+        <v>53.5</v>
+      </c>
+      <c r="H241">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="I241">
+        <v>736</v>
+      </c>
+      <c r="J241">
+        <v>478.65800000000002</v>
+      </c>
+      <c r="K241">
+        <v>0.36</v>
+      </c>
+      <c r="L241">
+        <v>7.65</v>
+      </c>
+      <c r="M241">
+        <v>24.22</v>
+      </c>
+      <c r="N241">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O241">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="P241">
+        <v>71.97</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>28</v>
+      </c>
+      <c r="R241" t="s">
+        <v>28</v>
+      </c>
+      <c r="S241" t="s">
+        <v>28</v>
+      </c>
+      <c r="T241" t="s">
+        <v>28</v>
+      </c>
+      <c r="U241" t="s">
+        <v>28</v>
+      </c>
+      <c r="V241" t="s">
+        <v>28</v>
+      </c>
+      <c r="W241" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>31</v>
+      </c>
+      <c r="C242" t="s">
+        <v>58</v>
+      </c>
+      <c r="D242" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E242" s="2">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="F242">
+        <v>18.581</v>
+      </c>
+      <c r="G242">
+        <v>83.4</v>
+      </c>
+      <c r="H242">
+        <v>7.79</v>
+      </c>
+      <c r="I242">
+        <v>536</v>
+      </c>
+      <c r="J242">
+        <v>348.31400000000002</v>
+      </c>
+      <c r="K242">
+        <v>0.26</v>
+      </c>
+      <c r="L242">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="M242">
+        <v>14.38</v>
+      </c>
+      <c r="N242">
+        <v>0.23</v>
+      </c>
+      <c r="O242">
+        <v>4.41</v>
+      </c>
+      <c r="P242">
+        <v>31.29</v>
+      </c>
+      <c r="Q242">
+        <v>5</v>
+      </c>
+      <c r="R242">
+        <v>30</v>
+      </c>
+      <c r="S242">
+        <v>4</v>
+      </c>
+      <c r="T242">
+        <v>44928</v>
+      </c>
+      <c r="U242">
+        <v>45721</v>
+      </c>
+      <c r="V242">
+        <v>793</v>
+      </c>
+      <c r="W242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>31</v>
+      </c>
+      <c r="C243" t="s">
+        <v>36</v>
+      </c>
+      <c r="D243" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E243" s="2">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="F243">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="G243">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="H243">
+        <v>5.98</v>
+      </c>
+      <c r="I243">
+        <v>580</v>
+      </c>
+      <c r="J243">
+        <v>377.15</v>
+      </c>
+      <c r="K243">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L243">
+        <v>7.82</v>
+      </c>
+      <c r="M243">
+        <v>24.5</v>
+      </c>
+      <c r="N243">
+        <v>0.31</v>
+      </c>
+      <c r="O243">
+        <v>4.53</v>
+      </c>
+      <c r="P243">
+        <v>45.9</v>
+      </c>
+      <c r="Q243">
+        <v>4</v>
+      </c>
+      <c r="R243">
+        <v>30</v>
+      </c>
+      <c r="S243">
+        <v>4</v>
+      </c>
+      <c r="T243">
+        <v>45908</v>
+      </c>
+      <c r="U243">
+        <v>46519</v>
+      </c>
+      <c r="V243">
+        <v>611</v>
+      </c>
+      <c r="W243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>31</v>
+      </c>
+      <c r="C244" t="s">
+        <v>37</v>
+      </c>
+      <c r="D244" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E244" s="2">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="F244">
+        <v>19.687000000000001</v>
+      </c>
+      <c r="G244">
+        <v>67</v>
+      </c>
+      <c r="H244">
+        <v>6.18</v>
+      </c>
+      <c r="I244">
+        <v>556</v>
+      </c>
+      <c r="J244">
+        <v>361.58100000000002</v>
+      </c>
+      <c r="K244">
+        <v>0.27</v>
+      </c>
+      <c r="L244">
+        <v>7.78</v>
+      </c>
+      <c r="M244">
+        <v>23.17</v>
+      </c>
+      <c r="N244">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O244">
+        <v>4.3</v>
+      </c>
+      <c r="P244">
+        <v>45.91</v>
+      </c>
+      <c r="Q244">
+        <v>4</v>
+      </c>
+      <c r="R244">
+        <v>30</v>
+      </c>
+      <c r="S244">
+        <v>4</v>
+      </c>
+      <c r="T244">
+        <v>46520</v>
+      </c>
+      <c r="U244">
+        <v>47174</v>
+      </c>
+      <c r="V244">
+        <v>654</v>
+      </c>
+      <c r="W244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>31</v>
+      </c>
+      <c r="C245" t="s">
+        <v>38</v>
+      </c>
+      <c r="D245" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E245" s="2">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="F245">
+        <v>19.975000000000001</v>
+      </c>
+      <c r="G245">
+        <v>61.5</v>
+      </c>
+      <c r="H245">
+        <v>5.58</v>
+      </c>
+      <c r="I245">
+        <v>545</v>
+      </c>
+      <c r="J245">
+        <v>354.05900000000003</v>
+      </c>
+      <c r="K245">
+        <v>0.26</v>
+      </c>
+      <c r="L245">
+        <v>7.75</v>
+      </c>
+      <c r="M245">
+        <v>15.27</v>
+      </c>
+      <c r="N245">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O245">
+        <v>2.92</v>
+      </c>
+      <c r="P245">
+        <v>54.32</v>
+      </c>
+      <c r="Q245">
+        <v>4</v>
+      </c>
+      <c r="R245">
+        <v>30</v>
+      </c>
+      <c r="S245">
+        <v>4</v>
+      </c>
+      <c r="T245">
+        <v>47704</v>
+      </c>
+      <c r="U245">
+        <v>48430</v>
+      </c>
+      <c r="V245">
+        <v>726</v>
+      </c>
+      <c r="W245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>31</v>
+      </c>
+      <c r="C246" t="s">
+        <v>39</v>
+      </c>
+      <c r="D246" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E246" s="2">
+        <v>0.46944444444444444</v>
+      </c>
+      <c r="F246">
+        <v>22.251999999999999</v>
+      </c>
+      <c r="G246">
+        <v>38.9</v>
+      </c>
+      <c r="H246">
+        <v>3.38</v>
+      </c>
+      <c r="I246">
+        <v>508</v>
+      </c>
+      <c r="J246">
+        <v>330.31599999999997</v>
+      </c>
+      <c r="K246">
+        <v>0.25</v>
+      </c>
+      <c r="L246">
+        <v>7.36</v>
+      </c>
+      <c r="M246">
+        <v>4.46</v>
+      </c>
+      <c r="N246">
+        <v>0.1</v>
+      </c>
+      <c r="O246">
+        <v>2.17</v>
+      </c>
+      <c r="P246">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="Q246">
+        <v>4.5</v>
+      </c>
+      <c r="R246">
+        <v>15</v>
+      </c>
+      <c r="S246">
+        <v>4</v>
+      </c>
+      <c r="T246" t="s">
+        <v>28</v>
+      </c>
+      <c r="U246" t="s">
+        <v>28</v>
+      </c>
+      <c r="V246" t="s">
+        <v>28</v>
+      </c>
+      <c r="W246">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Documents\R\Projects\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED490F51-98E7-4318-A759-26B47CE2FB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BFF2EE-8AA1-4920-8D59-41A0A0ED5C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="81">
   <si>
     <t>RowID</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>Sampled in EW fish passage channel</t>
+  </si>
+  <si>
+    <t>wq</t>
+  </si>
+  <si>
+    <t>ARC1</t>
+  </si>
+  <si>
+    <t>Backflow observed from Knaggs property to the KLRC channel near wq collection point just west of Wallace Weir.</t>
   </si>
 </sst>
 </file>
@@ -608,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z246"/>
+  <dimension ref="A1:Z258"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12.453125" customWidth="1"/>
@@ -17911,7 +17920,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -17982,7 +17991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -18053,7 +18062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -18124,7 +18133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -18195,7 +18204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -18266,7 +18275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -18334,6 +18343,861 @@
         <v>28</v>
       </c>
       <c r="W246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>31</v>
+      </c>
+      <c r="C247" t="s">
+        <v>32</v>
+      </c>
+      <c r="D247" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E247" s="2">
+        <v>0.31874999999999998</v>
+      </c>
+      <c r="F247">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="G247">
+        <v>93.3</v>
+      </c>
+      <c r="H247">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="I247">
+        <v>273.60000000000002</v>
+      </c>
+      <c r="J247">
+        <v>177.86600000000001</v>
+      </c>
+      <c r="K247">
+        <v>0.13</v>
+      </c>
+      <c r="L247">
+        <v>7.73</v>
+      </c>
+      <c r="M247">
+        <v>11.8</v>
+      </c>
+      <c r="N247">
+        <v>0.23</v>
+      </c>
+      <c r="O247">
+        <v>10.81</v>
+      </c>
+      <c r="P247">
+        <v>15.85</v>
+      </c>
+      <c r="Q247">
+        <v>2.5</v>
+      </c>
+      <c r="R247">
+        <v>30</v>
+      </c>
+      <c r="S247">
+        <v>4</v>
+      </c>
+      <c r="T247">
+        <v>201281</v>
+      </c>
+      <c r="U247">
+        <v>201883</v>
+      </c>
+      <c r="V247">
+        <v>602</v>
+      </c>
+      <c r="W247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>69</v>
+      </c>
+      <c r="C248" t="s">
+        <v>73</v>
+      </c>
+      <c r="D248" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E248" s="2">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="F248">
+        <v>21.085000000000001</v>
+      </c>
+      <c r="G248">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="H248">
+        <v>6.65</v>
+      </c>
+      <c r="I248">
+        <v>640</v>
+      </c>
+      <c r="J248">
+        <v>416.25</v>
+      </c>
+      <c r="K248">
+        <v>0.31</v>
+      </c>
+      <c r="L248">
+        <v>7.68</v>
+      </c>
+      <c r="M248">
+        <v>7.27</v>
+      </c>
+      <c r="N248">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O248">
+        <v>6.71</v>
+      </c>
+      <c r="P248">
+        <v>22.28</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>28</v>
+      </c>
+      <c r="R248" t="s">
+        <v>28</v>
+      </c>
+      <c r="S248" t="s">
+        <v>28</v>
+      </c>
+      <c r="T248" t="s">
+        <v>28</v>
+      </c>
+      <c r="U248" t="s">
+        <v>28</v>
+      </c>
+      <c r="V248" t="s">
+        <v>28</v>
+      </c>
+      <c r="W248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>31</v>
+      </c>
+      <c r="C249" t="s">
+        <v>34</v>
+      </c>
+      <c r="D249" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E249" s="2">
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="F249">
+        <v>21.084</v>
+      </c>
+      <c r="G249">
+        <v>69.8</v>
+      </c>
+      <c r="H249">
+        <v>6.2</v>
+      </c>
+      <c r="I249">
+        <v>623</v>
+      </c>
+      <c r="J249">
+        <v>404.80399999999997</v>
+      </c>
+      <c r="K249">
+        <v>0.3</v>
+      </c>
+      <c r="L249">
+        <v>7.61</v>
+      </c>
+      <c r="M249">
+        <v>5.83</v>
+      </c>
+      <c r="N249">
+        <v>0.12</v>
+      </c>
+      <c r="O249">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="P249">
+        <v>25.32</v>
+      </c>
+      <c r="Q249">
+        <v>3.5</v>
+      </c>
+      <c r="R249">
+        <v>30</v>
+      </c>
+      <c r="S249">
+        <v>4</v>
+      </c>
+      <c r="T249">
+        <v>201877</v>
+      </c>
+      <c r="U249">
+        <v>202849</v>
+      </c>
+      <c r="V249">
+        <v>972</v>
+      </c>
+      <c r="W249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>78</v>
+      </c>
+      <c r="C250" t="s">
+        <v>79</v>
+      </c>
+      <c r="D250" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E250" s="2">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="F250">
+        <v>19.725999999999999</v>
+      </c>
+      <c r="G250">
+        <v>53.1</v>
+      </c>
+      <c r="H250">
+        <v>4.84</v>
+      </c>
+      <c r="I250">
+        <v>638</v>
+      </c>
+      <c r="J250">
+        <v>414.68599999999998</v>
+      </c>
+      <c r="K250">
+        <v>0.31</v>
+      </c>
+      <c r="L250">
+        <v>7.37</v>
+      </c>
+      <c r="M250">
+        <v>21.82</v>
+      </c>
+      <c r="N250">
+        <v>0.23</v>
+      </c>
+      <c r="O250">
+        <v>11.51</v>
+      </c>
+      <c r="P250">
+        <v>55.25</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>28</v>
+      </c>
+      <c r="R250" t="s">
+        <v>28</v>
+      </c>
+      <c r="S250" t="s">
+        <v>28</v>
+      </c>
+      <c r="T250" t="s">
+        <v>28</v>
+      </c>
+      <c r="U250" t="s">
+        <v>28</v>
+      </c>
+      <c r="V250" t="s">
+        <v>28</v>
+      </c>
+      <c r="W250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>31</v>
+      </c>
+      <c r="C251" t="s">
+        <v>35</v>
+      </c>
+      <c r="D251" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E251" s="2">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="F251">
+        <v>20.033999999999999</v>
+      </c>
+      <c r="G251">
+        <v>84.7</v>
+      </c>
+      <c r="H251">
+        <v>7.68</v>
+      </c>
+      <c r="I251">
+        <v>914</v>
+      </c>
+      <c r="J251">
+        <v>593.85500000000002</v>
+      </c>
+      <c r="K251">
+        <v>0.45</v>
+      </c>
+      <c r="L251">
+        <v>7.97</v>
+      </c>
+      <c r="M251">
+        <v>19.91</v>
+      </c>
+      <c r="N251">
+        <v>0.25</v>
+      </c>
+      <c r="O251">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="P251">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="Q251">
+        <v>3</v>
+      </c>
+      <c r="R251">
+        <v>30</v>
+      </c>
+      <c r="S251">
+        <v>4</v>
+      </c>
+      <c r="T251">
+        <v>202492</v>
+      </c>
+      <c r="U251">
+        <v>203035</v>
+      </c>
+      <c r="V251">
+        <v>543</v>
+      </c>
+      <c r="W251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>31</v>
+      </c>
+      <c r="C252" t="s">
+        <v>51</v>
+      </c>
+      <c r="D252" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E252" s="2">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="F252">
+        <v>20.88</v>
+      </c>
+      <c r="G252">
+        <v>90.2</v>
+      </c>
+      <c r="H252">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="I252">
+        <v>956</v>
+      </c>
+      <c r="J252">
+        <v>621.39099999999996</v>
+      </c>
+      <c r="K252">
+        <v>0.47</v>
+      </c>
+      <c r="L252">
+        <v>8.26</v>
+      </c>
+      <c r="M252">
+        <v>8.65</v>
+      </c>
+      <c r="N252">
+        <v>0.09</v>
+      </c>
+      <c r="O252">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="P252">
+        <v>36.130000000000003</v>
+      </c>
+      <c r="Q252">
+        <v>2.5</v>
+      </c>
+      <c r="R252">
+        <v>15</v>
+      </c>
+      <c r="S252">
+        <v>4</v>
+      </c>
+      <c r="T252" t="s">
+        <v>28</v>
+      </c>
+      <c r="U252" t="s">
+        <v>28</v>
+      </c>
+      <c r="V252" t="s">
+        <v>28</v>
+      </c>
+      <c r="W252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>253</v>
+      </c>
+      <c r="B253" t="s">
+        <v>78</v>
+      </c>
+      <c r="C253" t="s">
+        <v>48</v>
+      </c>
+      <c r="D253" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E253" s="2">
+        <v>0.31458333333333333</v>
+      </c>
+      <c r="F253">
+        <v>19.936</v>
+      </c>
+      <c r="G253">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H253">
+        <v>1.78</v>
+      </c>
+      <c r="I253">
+        <v>1795</v>
+      </c>
+      <c r="J253">
+        <v>1167.037</v>
+      </c>
+      <c r="K253">
+        <v>0.91</v>
+      </c>
+      <c r="L253">
+        <v>8</v>
+      </c>
+      <c r="M253">
+        <v>8.77</v>
+      </c>
+      <c r="N253">
+        <v>0.21</v>
+      </c>
+      <c r="O253">
+        <v>4.17</v>
+      </c>
+      <c r="P253">
+        <v>117.49</v>
+      </c>
+      <c r="Q253">
+        <v>4</v>
+      </c>
+      <c r="R253">
+        <v>30</v>
+      </c>
+      <c r="S253">
+        <v>4</v>
+      </c>
+      <c r="T253">
+        <v>48487</v>
+      </c>
+      <c r="U253">
+        <v>48958</v>
+      </c>
+      <c r="V253">
+        <v>471</v>
+      </c>
+      <c r="W253">
+        <v>1</v>
+      </c>
+      <c r="Z253" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="254" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>254</v>
+      </c>
+      <c r="B254" t="s">
+        <v>31</v>
+      </c>
+      <c r="C254" t="s">
+        <v>58</v>
+      </c>
+      <c r="D254" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E254" s="2">
+        <v>0.33888888888888891</v>
+      </c>
+      <c r="F254">
+        <v>19.341999999999999</v>
+      </c>
+      <c r="G254">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="H254">
+        <v>7.2</v>
+      </c>
+      <c r="I254">
+        <v>816</v>
+      </c>
+      <c r="J254">
+        <v>530.73699999999997</v>
+      </c>
+      <c r="K254">
+        <v>0.4</v>
+      </c>
+      <c r="L254">
+        <v>8.11</v>
+      </c>
+      <c r="M254">
+        <v>28.92</v>
+      </c>
+      <c r="N254">
+        <v>0.3</v>
+      </c>
+      <c r="O254">
+        <v>8.36</v>
+      </c>
+      <c r="P254">
+        <v>28.81</v>
+      </c>
+      <c r="Q254">
+        <v>4.5</v>
+      </c>
+      <c r="R254">
+        <v>30</v>
+      </c>
+      <c r="S254">
+        <v>4</v>
+      </c>
+      <c r="T254">
+        <v>48959</v>
+      </c>
+      <c r="U254">
+        <v>49549</v>
+      </c>
+      <c r="V254">
+        <v>590</v>
+      </c>
+      <c r="W254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>255</v>
+      </c>
+      <c r="B255" t="s">
+        <v>31</v>
+      </c>
+      <c r="C255" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E255" s="2">
+        <v>0.38819444444444445</v>
+      </c>
+      <c r="F255">
+        <v>21.306000000000001</v>
+      </c>
+      <c r="G255">
+        <v>54.3</v>
+      </c>
+      <c r="H255">
+        <v>4.79</v>
+      </c>
+      <c r="I255">
+        <v>689</v>
+      </c>
+      <c r="J255">
+        <v>447.61399999999998</v>
+      </c>
+      <c r="K255">
+        <v>0.34</v>
+      </c>
+      <c r="L255">
+        <v>7.75</v>
+      </c>
+      <c r="M255">
+        <v>8.24</v>
+      </c>
+      <c r="N255">
+        <v>0.15</v>
+      </c>
+      <c r="O255">
+        <v>4.29</v>
+      </c>
+      <c r="P255">
+        <v>63.02</v>
+      </c>
+      <c r="Q255">
+        <v>3</v>
+      </c>
+      <c r="R255">
+        <v>30</v>
+      </c>
+      <c r="S255">
+        <v>4</v>
+      </c>
+      <c r="T255">
+        <v>49595</v>
+      </c>
+      <c r="U255">
+        <v>50085</v>
+      </c>
+      <c r="V255">
+        <v>490</v>
+      </c>
+      <c r="W255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>256</v>
+      </c>
+      <c r="B256" t="s">
+        <v>31</v>
+      </c>
+      <c r="C256" t="s">
+        <v>39</v>
+      </c>
+      <c r="D256" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E256" s="2">
+        <v>0.42569444444444443</v>
+      </c>
+      <c r="F256">
+        <v>19.036000000000001</v>
+      </c>
+      <c r="G256">
+        <v>43.3</v>
+      </c>
+      <c r="H256">
+        <v>4</v>
+      </c>
+      <c r="I256">
+        <v>594</v>
+      </c>
+      <c r="J256">
+        <v>386</v>
+      </c>
+      <c r="K256">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L256">
+        <v>7.55</v>
+      </c>
+      <c r="M256">
+        <v>6.98</v>
+      </c>
+      <c r="N256">
+        <v>0.31</v>
+      </c>
+      <c r="O256">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="P256">
+        <v>93.33</v>
+      </c>
+      <c r="Q256">
+        <v>5</v>
+      </c>
+      <c r="R256">
+        <v>15</v>
+      </c>
+      <c r="S256">
+        <v>4</v>
+      </c>
+      <c r="T256" t="s">
+        <v>28</v>
+      </c>
+      <c r="U256" t="s">
+        <v>28</v>
+      </c>
+      <c r="V256" t="s">
+        <v>28</v>
+      </c>
+      <c r="W256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A257">
+        <v>257</v>
+      </c>
+      <c r="B257" t="s">
+        <v>31</v>
+      </c>
+      <c r="C257" t="s">
+        <v>37</v>
+      </c>
+      <c r="D257" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E257" s="2">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="F257">
+        <v>21.63</v>
+      </c>
+      <c r="G257">
+        <v>53.6</v>
+      </c>
+      <c r="H257">
+        <v>4.71</v>
+      </c>
+      <c r="I257">
+        <v>778</v>
+      </c>
+      <c r="J257">
+        <v>505.78500000000003</v>
+      </c>
+      <c r="K257">
+        <v>0.38</v>
+      </c>
+      <c r="L257">
+        <v>7.75</v>
+      </c>
+      <c r="M257">
+        <v>14.25</v>
+      </c>
+      <c r="N257">
+        <v>0.43</v>
+      </c>
+      <c r="O257">
+        <v>9.08</v>
+      </c>
+      <c r="P257">
+        <v>55.42</v>
+      </c>
+      <c r="Q257">
+        <v>3</v>
+      </c>
+      <c r="R257">
+        <v>30</v>
+      </c>
+      <c r="S257">
+        <v>4</v>
+      </c>
+      <c r="T257">
+        <v>51792</v>
+      </c>
+      <c r="U257">
+        <v>52457</v>
+      </c>
+      <c r="V257">
+        <v>665</v>
+      </c>
+      <c r="W257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A258">
+        <v>258</v>
+      </c>
+      <c r="B258" t="s">
+        <v>31</v>
+      </c>
+      <c r="C258" t="s">
+        <v>36</v>
+      </c>
+      <c r="D258" s="1">
+        <v>46105</v>
+      </c>
+      <c r="E258" s="2">
+        <v>0.49513888888888891</v>
+      </c>
+      <c r="F258">
+        <v>22.888000000000002</v>
+      </c>
+      <c r="G258">
+        <v>53</v>
+      </c>
+      <c r="H258">
+        <v>4.54</v>
+      </c>
+      <c r="I258">
+        <v>860</v>
+      </c>
+      <c r="J258">
+        <v>559.26400000000001</v>
+      </c>
+      <c r="K258">
+        <v>0.42</v>
+      </c>
+      <c r="L258">
+        <v>7.79</v>
+      </c>
+      <c r="M258">
+        <v>16.59</v>
+      </c>
+      <c r="N258">
+        <v>0.2</v>
+      </c>
+      <c r="O258">
+        <v>4.47</v>
+      </c>
+      <c r="P258">
+        <v>51.61</v>
+      </c>
+      <c r="Q258">
+        <v>3</v>
+      </c>
+      <c r="R258">
+        <v>30</v>
+      </c>
+      <c r="S258">
+        <v>4</v>
+      </c>
+      <c r="T258">
+        <v>52458</v>
+      </c>
+      <c r="U258">
+        <v>53078</v>
+      </c>
+      <c r="V258">
+        <v>620</v>
+      </c>
+      <c r="W258">
         <v>1</v>
       </c>
     </row>

--- a/Data/tabular/YBLTE_point_wq.xlsx
+++ b/Data/tabular/YBLTE_point_wq.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eholmes\Documents\R\Projects\YBLTE\Data\tabular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BFF2EE-8AA1-4920-8D59-41A0A0ED5C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868B46B7-A140-47B4-AA0E-DDFE9C9462D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="115">
   <si>
     <t>RowID</t>
   </si>
@@ -279,6 +279,108 @@
   </si>
   <si>
     <t>Backflow observed from Knaggs property to the KLRC channel near wq collection point just west of Wallace Weir.</t>
+  </si>
+  <si>
+    <t>Adult carp observed downstream of siphon</t>
+  </si>
+  <si>
+    <t>Sampled in Sac R. upstream of intake channel since water was running north from Tule Pond.</t>
+  </si>
+  <si>
+    <t>Slight algal film on surface of water, maybe cyanobacteria bloom starting</t>
+  </si>
+  <si>
+    <t>KLWWALT</t>
+  </si>
+  <si>
+    <t>Sampled in ridgecut at start of Knaggs field 3</t>
+  </si>
+  <si>
+    <t>Draining, but loggers still in a few inches of water.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No water passing through Wallace Weir </t>
+  </si>
+  <si>
+    <t>Below Wallace Weir collection site</t>
+  </si>
+  <si>
+    <t>Very low flow &lt;5cfs</t>
+  </si>
+  <si>
+    <t>Water draining from Conaway supply canal.</t>
+  </si>
+  <si>
+    <t>Very zoopy, but mostly small-bodied zoop</t>
+  </si>
+  <si>
+    <t>Lots of small-bodied zoop</t>
+  </si>
+  <si>
+    <t>Very shallow, zoop sampling altered to avoid collecting substrate</t>
+  </si>
+  <si>
+    <t>Sampled in intake channel which was inundated, but not flowing.</t>
+  </si>
+  <si>
+    <t>Low flow (&lt;5 cfs). Curiosly, the woodland drain to the south was low, but had more flow.</t>
+  </si>
+  <si>
+    <t>Approzimately 400-800 cfs passing Wallace Weir</t>
+  </si>
+  <si>
+    <t>Very zoopy, with lots of small bodied critters</t>
+  </si>
+  <si>
+    <t>Sampled below Wallace Weir, small flow coming through fish passge structure (~20cfs)</t>
+  </si>
+  <si>
+    <t>No perceptable flow</t>
+  </si>
+  <si>
+    <t>WDSYB</t>
+  </si>
+  <si>
+    <t>Lots of flow coming from Woodland runoff. Sampled in the pool below the structure immediately south from CCSYB. Lots of drak particulate organic matter and some benthic algae. Zoop score difficult to estimate</t>
+  </si>
+  <si>
+    <t>CSBJ</t>
+  </si>
+  <si>
+    <t>~5-10cfs coming from cache and going through a road culvert. Could not tell if it was going through the levee structure south to the Woodland drainage ditch.</t>
+  </si>
+  <si>
+    <t>Low flow, much of it appears to be coming from Conaway supply ditch culverts.</t>
+  </si>
+  <si>
+    <t>Sampled in the Sac river.</t>
+  </si>
+  <si>
+    <t>This sample was anomalous to other Toe Drain samples. One factor that may be affecting it was that local runoff could be pumped in just uptream from West Sac at Lake Washington.</t>
+  </si>
+  <si>
+    <t>Very high tide. Flow was going over the weir.</t>
+  </si>
+  <si>
+    <t>Very low zoop which was a quic departure from last week's very zoopy sample.</t>
+  </si>
+  <si>
+    <t>Sampled below WW. Small flow coming through the fish collection facility.</t>
+  </si>
+  <si>
+    <t>Big notch open but flow is moving north out of Tule Pond. We sampled upstream of the intake channel in the Sac River.</t>
+  </si>
+  <si>
+    <t>Narrow sampling lane in the veg led to veg in the zoop net.</t>
+  </si>
+  <si>
+    <t>Very low tide.</t>
+  </si>
+  <si>
+    <t>ARC1N</t>
+  </si>
+  <si>
+    <t>ARC1S</t>
   </si>
 </sst>
 </file>
@@ -617,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z258"/>
+  <dimension ref="A1:Z306"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12.453125" customWidth="1"/>
@@ -19059,7 +19161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>257</v>
       </c>
@@ -19130,7 +19232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>258</v>
       </c>
@@ -19199,6 +19301,3504 @@
       </c>
       <c r="W258">
         <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A259">
+        <v>259</v>
+      </c>
+      <c r="B259" t="s">
+        <v>31</v>
+      </c>
+      <c r="C259" t="s">
+        <v>58</v>
+      </c>
+      <c r="D259" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E259" s="2">
+        <v>0.30486111111111114</v>
+      </c>
+      <c r="F259">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="G259">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="H259">
+        <v>6.94</v>
+      </c>
+      <c r="I259">
+        <v>753</v>
+      </c>
+      <c r="J259">
+        <v>489.47</v>
+      </c>
+      <c r="K259">
+        <v>0.37</v>
+      </c>
+      <c r="L259">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="M259">
+        <v>21.29</v>
+      </c>
+      <c r="N259">
+        <v>0.24</v>
+      </c>
+      <c r="O259">
+        <v>9.4</v>
+      </c>
+      <c r="P259">
+        <v>34.18</v>
+      </c>
+      <c r="Q259">
+        <v>4</v>
+      </c>
+      <c r="R259">
+        <v>30</v>
+      </c>
+      <c r="S259">
+        <v>4</v>
+      </c>
+      <c r="T259">
+        <v>203031</v>
+      </c>
+      <c r="U259">
+        <v>203619</v>
+      </c>
+      <c r="V259">
+        <v>588</v>
+      </c>
+      <c r="W259">
+        <v>1</v>
+      </c>
+      <c r="Z259" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="260" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A260">
+        <v>260</v>
+      </c>
+      <c r="B260" t="s">
+        <v>31</v>
+      </c>
+      <c r="C260" t="s">
+        <v>32</v>
+      </c>
+      <c r="D260" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E260" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F260">
+        <v>17.78</v>
+      </c>
+      <c r="G260">
+        <v>95.4</v>
+      </c>
+      <c r="H260">
+        <v>9.07</v>
+      </c>
+      <c r="I260">
+        <v>216</v>
+      </c>
+      <c r="J260">
+        <v>140.44999999999999</v>
+      </c>
+      <c r="K260">
+        <v>0.1</v>
+      </c>
+      <c r="L260">
+        <v>7.82</v>
+      </c>
+      <c r="M260">
+        <v>8.16</v>
+      </c>
+      <c r="N260">
+        <v>0.12</v>
+      </c>
+      <c r="O260">
+        <v>4.55</v>
+      </c>
+      <c r="P260">
+        <v>12.84</v>
+      </c>
+      <c r="Q260">
+        <v>2</v>
+      </c>
+      <c r="R260">
+        <v>30</v>
+      </c>
+      <c r="S260">
+        <v>4</v>
+      </c>
+      <c r="T260">
+        <v>203619</v>
+      </c>
+      <c r="U260">
+        <v>204180</v>
+      </c>
+      <c r="V260">
+        <v>561</v>
+      </c>
+      <c r="W260">
+        <v>1</v>
+      </c>
+      <c r="Z260" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="261" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A261">
+        <v>261</v>
+      </c>
+      <c r="B261" t="s">
+        <v>31</v>
+      </c>
+      <c r="C261" t="s">
+        <v>34</v>
+      </c>
+      <c r="D261" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E261" s="2">
+        <v>0.35138888888888886</v>
+      </c>
+      <c r="F261">
+        <v>20.93</v>
+      </c>
+      <c r="G261">
+        <v>75</v>
+      </c>
+      <c r="H261">
+        <v>6.68</v>
+      </c>
+      <c r="I261">
+        <v>662</v>
+      </c>
+      <c r="J261">
+        <v>430.48</v>
+      </c>
+      <c r="K261">
+        <v>0.32</v>
+      </c>
+      <c r="L261">
+        <v>7.71</v>
+      </c>
+      <c r="M261">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="N261">
+        <v>1.29</v>
+      </c>
+      <c r="O261">
+        <v>3.6</v>
+      </c>
+      <c r="P261">
+        <v>24.43</v>
+      </c>
+      <c r="Q261">
+        <v>4</v>
+      </c>
+      <c r="R261">
+        <v>30</v>
+      </c>
+      <c r="S261">
+        <v>4</v>
+      </c>
+      <c r="T261">
+        <v>204180</v>
+      </c>
+      <c r="U261">
+        <v>204733</v>
+      </c>
+      <c r="V261">
+        <v>553</v>
+      </c>
+      <c r="W261">
+        <v>1</v>
+      </c>
+      <c r="Z261" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="262" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A262">
+        <v>262</v>
+      </c>
+      <c r="B262" t="s">
+        <v>31</v>
+      </c>
+      <c r="C262" t="s">
+        <v>35</v>
+      </c>
+      <c r="D262" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E262" s="2">
+        <v>0.38819444444444445</v>
+      </c>
+      <c r="F262">
+        <v>19.91</v>
+      </c>
+      <c r="G262">
+        <v>72.2</v>
+      </c>
+      <c r="H262">
+        <v>6.56</v>
+      </c>
+      <c r="I262">
+        <v>705</v>
+      </c>
+      <c r="J262">
+        <v>458.08</v>
+      </c>
+      <c r="K262">
+        <v>0.34</v>
+      </c>
+      <c r="L262">
+        <v>7.76</v>
+      </c>
+      <c r="M262">
+        <v>2.36</v>
+      </c>
+      <c r="N262">
+        <v>0.37</v>
+      </c>
+      <c r="O262">
+        <v>11.58</v>
+      </c>
+      <c r="P262">
+        <v>48.18</v>
+      </c>
+      <c r="Q262">
+        <v>4</v>
+      </c>
+      <c r="R262">
+        <v>30</v>
+      </c>
+      <c r="S262">
+        <v>4</v>
+      </c>
+      <c r="T262">
+        <v>204733</v>
+      </c>
+      <c r="U262">
+        <v>205299</v>
+      </c>
+      <c r="V262">
+        <v>566</v>
+      </c>
+      <c r="W262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A263">
+        <v>263</v>
+      </c>
+      <c r="B263" t="s">
+        <v>78</v>
+      </c>
+      <c r="C263" t="s">
+        <v>84</v>
+      </c>
+      <c r="D263" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E263" s="2">
+        <v>0.31041666666666667</v>
+      </c>
+      <c r="F263">
+        <v>19.341999999999999</v>
+      </c>
+      <c r="G263">
+        <v>50</v>
+      </c>
+      <c r="H263">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I263">
+        <v>608</v>
+      </c>
+      <c r="J263">
+        <v>395.37799999999999</v>
+      </c>
+      <c r="K263">
+        <v>0.3</v>
+      </c>
+      <c r="L263">
+        <v>7.51</v>
+      </c>
+      <c r="M263">
+        <v>22.85</v>
+      </c>
+      <c r="N263">
+        <v>0.74</v>
+      </c>
+      <c r="O263">
+        <v>17.829999999999998</v>
+      </c>
+      <c r="P263">
+        <v>60.81</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>28</v>
+      </c>
+      <c r="R263" t="s">
+        <v>28</v>
+      </c>
+      <c r="S263" t="s">
+        <v>28</v>
+      </c>
+      <c r="T263" t="s">
+        <v>28</v>
+      </c>
+      <c r="U263" t="s">
+        <v>28</v>
+      </c>
+      <c r="V263" t="s">
+        <v>28</v>
+      </c>
+      <c r="W263" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z263" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="264" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A264">
+        <v>264</v>
+      </c>
+      <c r="B264" t="s">
+        <v>31</v>
+      </c>
+      <c r="C264" t="s">
+        <v>48</v>
+      </c>
+      <c r="D264" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E264" s="2">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="F264">
+        <v>19.093</v>
+      </c>
+      <c r="G264">
+        <v>46.7</v>
+      </c>
+      <c r="H264">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="I264">
+        <v>677</v>
+      </c>
+      <c r="J264">
+        <v>439.96</v>
+      </c>
+      <c r="K264">
+        <v>0.33</v>
+      </c>
+      <c r="L264">
+        <v>7.54</v>
+      </c>
+      <c r="M264">
+        <v>16.8</v>
+      </c>
+      <c r="N264">
+        <v>0.69</v>
+      </c>
+      <c r="O264">
+        <v>17.27</v>
+      </c>
+      <c r="P264">
+        <v>67.02</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>28</v>
+      </c>
+      <c r="R264" t="s">
+        <v>28</v>
+      </c>
+      <c r="S264" t="s">
+        <v>28</v>
+      </c>
+      <c r="T264" t="s">
+        <v>28</v>
+      </c>
+      <c r="U264" t="s">
+        <v>28</v>
+      </c>
+      <c r="V264" t="s">
+        <v>28</v>
+      </c>
+      <c r="W264" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="265" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A265">
+        <v>265</v>
+      </c>
+      <c r="B265" t="s">
+        <v>31</v>
+      </c>
+      <c r="C265" t="s">
+        <v>36</v>
+      </c>
+      <c r="D265" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E265" s="2">
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="F265">
+        <v>20.59</v>
+      </c>
+      <c r="G265">
+        <v>59.1</v>
+      </c>
+      <c r="H265">
+        <v>5.34</v>
+      </c>
+      <c r="I265">
+        <v>745</v>
+      </c>
+      <c r="J265">
+        <v>484.14100000000002</v>
+      </c>
+      <c r="K265">
+        <v>0.36</v>
+      </c>
+      <c r="L265">
+        <v>7.81</v>
+      </c>
+      <c r="M265">
+        <v>24.59</v>
+      </c>
+      <c r="N265">
+        <v>0.41</v>
+      </c>
+      <c r="O265">
+        <v>8.48</v>
+      </c>
+      <c r="P265">
+        <v>47.64</v>
+      </c>
+      <c r="Q265">
+        <v>3</v>
+      </c>
+      <c r="R265">
+        <v>30</v>
+      </c>
+      <c r="S265">
+        <v>4</v>
+      </c>
+      <c r="T265">
+        <v>53130</v>
+      </c>
+      <c r="U265">
+        <v>53684</v>
+      </c>
+      <c r="V265">
+        <v>554</v>
+      </c>
+      <c r="W265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A266">
+        <v>266</v>
+      </c>
+      <c r="B266" t="s">
+        <v>31</v>
+      </c>
+      <c r="C266" t="s">
+        <v>37</v>
+      </c>
+      <c r="D266" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E266" s="2">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="F266">
+        <v>20.18</v>
+      </c>
+      <c r="G266">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="H266">
+        <v>5.93</v>
+      </c>
+      <c r="I266">
+        <v>790</v>
+      </c>
+      <c r="J266">
+        <v>513.36199999999997</v>
+      </c>
+      <c r="K266">
+        <v>0.39</v>
+      </c>
+      <c r="L266">
+        <v>7.87</v>
+      </c>
+      <c r="M266">
+        <v>19.55</v>
+      </c>
+      <c r="N266">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O266">
+        <v>13.32</v>
+      </c>
+      <c r="P266">
+        <v>46.03</v>
+      </c>
+      <c r="Q266">
+        <v>3</v>
+      </c>
+      <c r="R266">
+        <v>30</v>
+      </c>
+      <c r="S266">
+        <v>4</v>
+      </c>
+      <c r="T266">
+        <v>53838</v>
+      </c>
+      <c r="U266">
+        <v>54528</v>
+      </c>
+      <c r="V266">
+        <v>690</v>
+      </c>
+      <c r="W266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A267">
+        <v>267</v>
+      </c>
+      <c r="B267" t="s">
+        <v>31</v>
+      </c>
+      <c r="C267" t="s">
+        <v>38</v>
+      </c>
+      <c r="D267" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E267" s="2">
+        <v>0.41111111111111109</v>
+      </c>
+      <c r="F267">
+        <v>20.218</v>
+      </c>
+      <c r="G267">
+        <v>55</v>
+      </c>
+      <c r="H267">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="I267">
+        <v>869</v>
+      </c>
+      <c r="J267">
+        <v>564.81399999999996</v>
+      </c>
+      <c r="K267">
+        <v>0.43</v>
+      </c>
+      <c r="L267">
+        <v>7.7</v>
+      </c>
+      <c r="M267">
+        <v>11</v>
+      </c>
+      <c r="N267">
+        <v>0.22</v>
+      </c>
+      <c r="O267">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="P267">
+        <v>58.13</v>
+      </c>
+      <c r="Q267">
+        <v>3.5</v>
+      </c>
+      <c r="R267">
+        <v>30</v>
+      </c>
+      <c r="S267">
+        <v>4</v>
+      </c>
+      <c r="T267">
+        <v>54524</v>
+      </c>
+      <c r="U267">
+        <v>55128</v>
+      </c>
+      <c r="V267">
+        <v>604</v>
+      </c>
+      <c r="W267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A268">
+        <v>268</v>
+      </c>
+      <c r="B268" t="s">
+        <v>31</v>
+      </c>
+      <c r="C268" t="s">
+        <v>39</v>
+      </c>
+      <c r="D268" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E268" s="2">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="F268">
+        <v>20.495999999999999</v>
+      </c>
+      <c r="G268">
+        <v>40.4</v>
+      </c>
+      <c r="H268">
+        <v>3.63</v>
+      </c>
+      <c r="I268">
+        <v>559</v>
+      </c>
+      <c r="J268">
+        <v>363.05</v>
+      </c>
+      <c r="K268">
+        <v>0.27</v>
+      </c>
+      <c r="L268">
+        <v>7.29</v>
+      </c>
+      <c r="M268">
+        <v>10.7</v>
+      </c>
+      <c r="N268">
+        <v>0.34</v>
+      </c>
+      <c r="O268">
+        <v>5.15</v>
+      </c>
+      <c r="P268">
+        <v>79.2</v>
+      </c>
+      <c r="Q268">
+        <v>3.5</v>
+      </c>
+      <c r="R268">
+        <v>15</v>
+      </c>
+      <c r="S268">
+        <v>4</v>
+      </c>
+      <c r="T268" t="s">
+        <v>28</v>
+      </c>
+      <c r="U268" t="s">
+        <v>28</v>
+      </c>
+      <c r="V268" t="s">
+        <v>28</v>
+      </c>
+      <c r="W268">
+        <v>1</v>
+      </c>
+      <c r="Z268" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="269" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A269">
+        <v>269</v>
+      </c>
+      <c r="B269" t="s">
+        <v>31</v>
+      </c>
+      <c r="C269" t="s">
+        <v>48</v>
+      </c>
+      <c r="D269" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E269" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="F269">
+        <v>16.876000000000001</v>
+      </c>
+      <c r="G269">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="H269">
+        <v>3.88</v>
+      </c>
+      <c r="I269">
+        <v>1157</v>
+      </c>
+      <c r="J269">
+        <v>752.36199999999997</v>
+      </c>
+      <c r="K269">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L269">
+        <v>7.6</v>
+      </c>
+      <c r="M269">
+        <v>20.87</v>
+      </c>
+      <c r="N269">
+        <v>0.84</v>
+      </c>
+      <c r="O269">
+        <v>16.63</v>
+      </c>
+      <c r="P269">
+        <v>74.5</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>28</v>
+      </c>
+      <c r="R269" t="s">
+        <v>28</v>
+      </c>
+      <c r="S269" t="s">
+        <v>28</v>
+      </c>
+      <c r="T269" t="s">
+        <v>28</v>
+      </c>
+      <c r="U269" t="s">
+        <v>28</v>
+      </c>
+      <c r="V269" t="s">
+        <v>28</v>
+      </c>
+      <c r="W269" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z269" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="270" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A270">
+        <v>270</v>
+      </c>
+      <c r="B270" t="s">
+        <v>78</v>
+      </c>
+      <c r="C270" t="s">
+        <v>84</v>
+      </c>
+      <c r="D270" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E270" s="2">
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="F270">
+        <v>16.942</v>
+      </c>
+      <c r="G270">
+        <v>41.1</v>
+      </c>
+      <c r="H270">
+        <v>3.97</v>
+      </c>
+      <c r="I270">
+        <v>1018</v>
+      </c>
+      <c r="J270">
+        <v>661.28499999999997</v>
+      </c>
+      <c r="K270">
+        <v>0.51</v>
+      </c>
+      <c r="L270">
+        <v>7.58</v>
+      </c>
+      <c r="M270">
+        <v>20.2</v>
+      </c>
+      <c r="N270">
+        <v>0.81</v>
+      </c>
+      <c r="O270">
+        <v>17.68</v>
+      </c>
+      <c r="P270">
+        <v>70.87</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>28</v>
+      </c>
+      <c r="R270" t="s">
+        <v>28</v>
+      </c>
+      <c r="S270" t="s">
+        <v>28</v>
+      </c>
+      <c r="T270" t="s">
+        <v>28</v>
+      </c>
+      <c r="U270" t="s">
+        <v>28</v>
+      </c>
+      <c r="V270" t="s">
+        <v>28</v>
+      </c>
+      <c r="W270" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z270" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="271" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A271">
+        <v>271</v>
+      </c>
+      <c r="B271" t="s">
+        <v>31</v>
+      </c>
+      <c r="C271" t="s">
+        <v>58</v>
+      </c>
+      <c r="D271" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E271" s="2">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="F271">
+        <v>16.151</v>
+      </c>
+      <c r="G271">
+        <v>48.83</v>
+      </c>
+      <c r="H271">
+        <v>4.74</v>
+      </c>
+      <c r="I271">
+        <v>1141</v>
+      </c>
+      <c r="J271">
+        <v>741.59199999999998</v>
+      </c>
+      <c r="K271">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L271">
+        <v>7.63</v>
+      </c>
+      <c r="M271">
+        <v>35.89</v>
+      </c>
+      <c r="N271">
+        <v>0.34</v>
+      </c>
+      <c r="O271">
+        <v>5.49</v>
+      </c>
+      <c r="P271">
+        <v>56.64</v>
+      </c>
+      <c r="Q271">
+        <v>2</v>
+      </c>
+      <c r="R271">
+        <v>30</v>
+      </c>
+      <c r="S271">
+        <v>4</v>
+      </c>
+      <c r="T271">
+        <v>205304</v>
+      </c>
+      <c r="U271">
+        <v>205891</v>
+      </c>
+      <c r="V271">
+        <v>587</v>
+      </c>
+      <c r="W271">
+        <v>1</v>
+      </c>
+      <c r="Z271" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="272" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A272">
+        <v>272</v>
+      </c>
+      <c r="B272" t="s">
+        <v>31</v>
+      </c>
+      <c r="C272" t="s">
+        <v>35</v>
+      </c>
+      <c r="D272" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E272" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F272">
+        <v>18.084</v>
+      </c>
+      <c r="G272">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="H272">
+        <v>6.7</v>
+      </c>
+      <c r="I272">
+        <v>870</v>
+      </c>
+      <c r="J272">
+        <v>565.29300000000001</v>
+      </c>
+      <c r="K272">
+        <v>0.43</v>
+      </c>
+      <c r="L272">
+        <v>7.77</v>
+      </c>
+      <c r="M272">
+        <v>22.72</v>
+      </c>
+      <c r="N272">
+        <v>0.62</v>
+      </c>
+      <c r="O272">
+        <v>11.78</v>
+      </c>
+      <c r="P272">
+        <v>57.32</v>
+      </c>
+      <c r="Q272">
+        <v>4</v>
+      </c>
+      <c r="R272">
+        <v>30</v>
+      </c>
+      <c r="S272">
+        <v>4</v>
+      </c>
+      <c r="T272">
+        <v>205891</v>
+      </c>
+      <c r="U272">
+        <v>206446</v>
+      </c>
+      <c r="V272">
+        <v>555</v>
+      </c>
+      <c r="W272">
+        <v>1</v>
+      </c>
+      <c r="Z272" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="273" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A273">
+        <v>273</v>
+      </c>
+      <c r="B273" t="s">
+        <v>31</v>
+      </c>
+      <c r="C273" t="s">
+        <v>32</v>
+      </c>
+      <c r="D273" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E273" s="2">
+        <v>0.37569444444444444</v>
+      </c>
+      <c r="F273">
+        <v>16.986000000000001</v>
+      </c>
+      <c r="G273">
+        <v>99</v>
+      </c>
+      <c r="H273">
+        <v>9.57</v>
+      </c>
+      <c r="I273">
+        <v>213.1</v>
+      </c>
+      <c r="J273">
+        <v>138.53</v>
+      </c>
+      <c r="K273">
+        <v>0.1</v>
+      </c>
+      <c r="L273">
+        <v>7.99</v>
+      </c>
+      <c r="M273">
+        <v>5.88</v>
+      </c>
+      <c r="N273">
+        <v>0.21</v>
+      </c>
+      <c r="O273">
+        <v>3.98</v>
+      </c>
+      <c r="P273">
+        <v>16.98</v>
+      </c>
+      <c r="Q273">
+        <v>1.5</v>
+      </c>
+      <c r="R273">
+        <v>30</v>
+      </c>
+      <c r="S273">
+        <v>4</v>
+      </c>
+      <c r="T273">
+        <v>206603</v>
+      </c>
+      <c r="U273">
+        <v>207179</v>
+      </c>
+      <c r="V273">
+        <v>576</v>
+      </c>
+      <c r="W273">
+        <v>1</v>
+      </c>
+      <c r="Z273" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="274" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A274">
+        <v>274</v>
+      </c>
+      <c r="B274" t="s">
+        <v>31</v>
+      </c>
+      <c r="C274" t="s">
+        <v>34</v>
+      </c>
+      <c r="D274" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E274" s="2">
+        <v>0.39444444444444443</v>
+      </c>
+      <c r="F274">
+        <v>18.634</v>
+      </c>
+      <c r="G274">
+        <v>90.5</v>
+      </c>
+      <c r="H274">
+        <v>8.44</v>
+      </c>
+      <c r="I274">
+        <v>704</v>
+      </c>
+      <c r="J274">
+        <v>457.61799999999999</v>
+      </c>
+      <c r="K274">
+        <v>0.34</v>
+      </c>
+      <c r="L274">
+        <v>7.95</v>
+      </c>
+      <c r="M274">
+        <v>10.88</v>
+      </c>
+      <c r="N274">
+        <v>1.94</v>
+      </c>
+      <c r="O274">
+        <v>1.8</v>
+      </c>
+      <c r="P274">
+        <v>27.27</v>
+      </c>
+      <c r="Q274">
+        <v>4.5</v>
+      </c>
+      <c r="R274">
+        <v>30</v>
+      </c>
+      <c r="S274">
+        <v>4</v>
+      </c>
+      <c r="T274">
+        <v>207179</v>
+      </c>
+      <c r="U274">
+        <v>207768</v>
+      </c>
+      <c r="V274">
+        <v>589</v>
+      </c>
+      <c r="W274">
+        <v>1</v>
+      </c>
+      <c r="Z274" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="275" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A275">
+        <v>275</v>
+      </c>
+      <c r="B275" t="s">
+        <v>31</v>
+      </c>
+      <c r="C275" t="s">
+        <v>36</v>
+      </c>
+      <c r="D275" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E275" s="2">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="F275">
+        <v>21.135999999999999</v>
+      </c>
+      <c r="G275">
+        <v>75.3</v>
+      </c>
+      <c r="H275">
+        <v>6.68</v>
+      </c>
+      <c r="I275">
+        <v>862</v>
+      </c>
+      <c r="J275">
+        <v>560.24599999999998</v>
+      </c>
+      <c r="K275">
+        <v>0.42</v>
+      </c>
+      <c r="L275">
+        <v>7.83</v>
+      </c>
+      <c r="M275">
+        <v>25.51</v>
+      </c>
+      <c r="N275">
+        <v>0.54</v>
+      </c>
+      <c r="O275">
+        <v>10.3</v>
+      </c>
+      <c r="P275">
+        <v>49.41</v>
+      </c>
+      <c r="Q275">
+        <v>4</v>
+      </c>
+      <c r="R275">
+        <v>30</v>
+      </c>
+      <c r="S275">
+        <v>4</v>
+      </c>
+      <c r="T275">
+        <v>207768</v>
+      </c>
+      <c r="U275">
+        <v>208397</v>
+      </c>
+      <c r="V275">
+        <v>629</v>
+      </c>
+      <c r="W275">
+        <v>1</v>
+      </c>
+      <c r="Z275" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="276" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A276">
+        <v>276</v>
+      </c>
+      <c r="B276" t="s">
+        <v>31</v>
+      </c>
+      <c r="C276" t="s">
+        <v>79</v>
+      </c>
+      <c r="D276" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E276" s="2">
+        <v>0.40625</v>
+      </c>
+      <c r="F276">
+        <v>17.864999999999998</v>
+      </c>
+      <c r="G276">
+        <v>75.3</v>
+      </c>
+      <c r="H276">
+        <v>6.68</v>
+      </c>
+      <c r="I276">
+        <v>667</v>
+      </c>
+      <c r="J276">
+        <v>433.33199999999999</v>
+      </c>
+      <c r="K276">
+        <v>0.33</v>
+      </c>
+      <c r="L276">
+        <v>7.72</v>
+      </c>
+      <c r="M276">
+        <v>18.57</v>
+      </c>
+      <c r="N276">
+        <v>0.52</v>
+      </c>
+      <c r="O276">
+        <v>10.33</v>
+      </c>
+      <c r="P276">
+        <v>62.08</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>28</v>
+      </c>
+      <c r="R276" t="s">
+        <v>28</v>
+      </c>
+      <c r="S276" t="s">
+        <v>28</v>
+      </c>
+      <c r="T276" t="s">
+        <v>28</v>
+      </c>
+      <c r="U276" t="s">
+        <v>28</v>
+      </c>
+      <c r="V276" t="s">
+        <v>28</v>
+      </c>
+      <c r="W276" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="277" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A277">
+        <v>277</v>
+      </c>
+      <c r="B277" t="s">
+        <v>31</v>
+      </c>
+      <c r="C277" t="s">
+        <v>37</v>
+      </c>
+      <c r="D277" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E277" s="2">
+        <v>0.46597222222222223</v>
+      </c>
+      <c r="F277">
+        <v>18.646000000000001</v>
+      </c>
+      <c r="G277">
+        <v>70.3</v>
+      </c>
+      <c r="H277">
+        <v>6.56</v>
+      </c>
+      <c r="I277">
+        <v>679</v>
+      </c>
+      <c r="J277">
+        <v>441.57499999999999</v>
+      </c>
+      <c r="K277">
+        <v>0.33</v>
+      </c>
+      <c r="L277">
+        <v>7.85</v>
+      </c>
+      <c r="M277">
+        <v>20.74</v>
+      </c>
+      <c r="N277">
+        <v>0.49</v>
+      </c>
+      <c r="O277">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="P277">
+        <v>45.84</v>
+      </c>
+      <c r="Q277">
+        <v>3</v>
+      </c>
+      <c r="R277">
+        <v>30</v>
+      </c>
+      <c r="S277">
+        <v>4</v>
+      </c>
+      <c r="T277">
+        <v>208397</v>
+      </c>
+      <c r="U277">
+        <v>209033</v>
+      </c>
+      <c r="V277">
+        <v>636</v>
+      </c>
+      <c r="W277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A278">
+        <v>278</v>
+      </c>
+      <c r="B278" t="s">
+        <v>31</v>
+      </c>
+      <c r="C278" t="s">
+        <v>38</v>
+      </c>
+      <c r="D278" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E278" s="2">
+        <v>0.48749999999999999</v>
+      </c>
+      <c r="F278">
+        <v>19.47</v>
+      </c>
+      <c r="G278">
+        <v>80.2</v>
+      </c>
+      <c r="H278">
+        <v>7.36</v>
+      </c>
+      <c r="I278">
+        <v>671</v>
+      </c>
+      <c r="J278">
+        <v>436.35399999999998</v>
+      </c>
+      <c r="K278">
+        <v>0.33</v>
+      </c>
+      <c r="L278">
+        <v>8</v>
+      </c>
+      <c r="M278">
+        <v>11.22</v>
+      </c>
+      <c r="N278">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O278">
+        <v>1.87</v>
+      </c>
+      <c r="P278">
+        <v>47.16</v>
+      </c>
+      <c r="Q278">
+        <v>2.5</v>
+      </c>
+      <c r="R278">
+        <v>30</v>
+      </c>
+      <c r="S278">
+        <v>4</v>
+      </c>
+      <c r="T278">
+        <v>209033</v>
+      </c>
+      <c r="U278">
+        <v>209616</v>
+      </c>
+      <c r="V278">
+        <v>583</v>
+      </c>
+      <c r="W278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A279">
+        <v>279</v>
+      </c>
+      <c r="B279" t="s">
+        <v>31</v>
+      </c>
+      <c r="C279" t="s">
+        <v>39</v>
+      </c>
+      <c r="D279" s="1">
+        <v>46119</v>
+      </c>
+      <c r="E279" s="2">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="F279">
+        <v>22.010999999999999</v>
+      </c>
+      <c r="G279">
+        <v>100.5</v>
+      </c>
+      <c r="H279">
+        <v>8.77</v>
+      </c>
+      <c r="I279">
+        <v>589</v>
+      </c>
+      <c r="J279">
+        <v>383.149</v>
+      </c>
+      <c r="K279">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L279">
+        <v>7.53</v>
+      </c>
+      <c r="M279">
+        <v>8.15</v>
+      </c>
+      <c r="N279">
+        <v>0.36</v>
+      </c>
+      <c r="O279">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="P279">
+        <v>87.4</v>
+      </c>
+      <c r="Q279">
+        <v>4</v>
+      </c>
+      <c r="R279">
+        <v>15</v>
+      </c>
+      <c r="S279">
+        <v>4</v>
+      </c>
+      <c r="T279" t="s">
+        <v>28</v>
+      </c>
+      <c r="U279" t="s">
+        <v>28</v>
+      </c>
+      <c r="V279" t="s">
+        <v>28</v>
+      </c>
+      <c r="W279">
+        <v>0.8</v>
+      </c>
+      <c r="Z279" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="280" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A280">
+        <v>280</v>
+      </c>
+      <c r="B280" t="s">
+        <v>31</v>
+      </c>
+      <c r="C280" t="s">
+        <v>32</v>
+      </c>
+      <c r="D280" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E280" s="2">
+        <v>0.30694444444444446</v>
+      </c>
+      <c r="F280">
+        <v>15.436</v>
+      </c>
+      <c r="G280">
+        <v>90.8</v>
+      </c>
+      <c r="H280">
+        <v>9.07</v>
+      </c>
+      <c r="I280">
+        <v>150.4</v>
+      </c>
+      <c r="J280">
+        <v>97.731999999999999</v>
+      </c>
+      <c r="K280">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L280">
+        <v>7.76</v>
+      </c>
+      <c r="M280">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="N280">
+        <v>0.34</v>
+      </c>
+      <c r="O280">
+        <v>2.41</v>
+      </c>
+      <c r="P280">
+        <v>10.76</v>
+      </c>
+      <c r="Q280">
+        <v>1</v>
+      </c>
+      <c r="R280">
+        <v>30</v>
+      </c>
+      <c r="S280">
+        <v>4</v>
+      </c>
+      <c r="T280">
+        <v>210140</v>
+      </c>
+      <c r="U280">
+        <v>210710</v>
+      </c>
+      <c r="V280">
+        <v>570</v>
+      </c>
+      <c r="W280">
+        <v>1</v>
+      </c>
+      <c r="Z280" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="281" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A281">
+        <v>281</v>
+      </c>
+      <c r="B281" t="s">
+        <v>31</v>
+      </c>
+      <c r="C281" t="s">
+        <v>34</v>
+      </c>
+      <c r="D281" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E281" s="2">
+        <v>0.32430555555555557</v>
+      </c>
+      <c r="F281">
+        <v>17.091000000000001</v>
+      </c>
+      <c r="G281">
+        <v>84.2</v>
+      </c>
+      <c r="H281">
+        <v>8.08</v>
+      </c>
+      <c r="I281">
+        <v>712</v>
+      </c>
+      <c r="J281">
+        <v>463.66800000000001</v>
+      </c>
+      <c r="K281">
+        <v>0.35</v>
+      </c>
+      <c r="L281">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="M281">
+        <v>10.31</v>
+      </c>
+      <c r="N281">
+        <v>2.12</v>
+      </c>
+      <c r="O281">
+        <v>3.49</v>
+      </c>
+      <c r="P281">
+        <v>28.15</v>
+      </c>
+      <c r="Q281">
+        <v>3.5</v>
+      </c>
+      <c r="R281">
+        <v>30</v>
+      </c>
+      <c r="S281">
+        <v>4</v>
+      </c>
+      <c r="T281">
+        <v>210711</v>
+      </c>
+      <c r="U281">
+        <v>211313</v>
+      </c>
+      <c r="V281">
+        <v>602</v>
+      </c>
+      <c r="W281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A282">
+        <v>282</v>
+      </c>
+      <c r="B282" t="s">
+        <v>31</v>
+      </c>
+      <c r="C282" t="s">
+        <v>35</v>
+      </c>
+      <c r="D282" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E282" s="2">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="F282">
+        <v>16.898</v>
+      </c>
+      <c r="G282">
+        <v>70.2</v>
+      </c>
+      <c r="H282">
+        <v>6.79</v>
+      </c>
+      <c r="I282">
+        <v>562</v>
+      </c>
+      <c r="J282">
+        <v>365.47500000000002</v>
+      </c>
+      <c r="K282">
+        <v>0.27</v>
+      </c>
+      <c r="L282">
+        <v>7.75</v>
+      </c>
+      <c r="M282">
+        <v>27.35</v>
+      </c>
+      <c r="N282">
+        <v>0.44</v>
+      </c>
+      <c r="O282">
+        <v>7.46</v>
+      </c>
+      <c r="P282">
+        <v>60.45</v>
+      </c>
+      <c r="Q282">
+        <v>2.5</v>
+      </c>
+      <c r="R282">
+        <v>30</v>
+      </c>
+      <c r="S282">
+        <v>4</v>
+      </c>
+      <c r="T282">
+        <v>211313</v>
+      </c>
+      <c r="U282">
+        <v>211966</v>
+      </c>
+      <c r="V282">
+        <v>653</v>
+      </c>
+      <c r="W282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A283">
+        <v>283</v>
+      </c>
+      <c r="B283" t="s">
+        <v>31</v>
+      </c>
+      <c r="C283" t="s">
+        <v>58</v>
+      </c>
+      <c r="D283" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E283" s="2">
+        <v>0.36388888888888887</v>
+      </c>
+      <c r="F283">
+        <v>15.73</v>
+      </c>
+      <c r="G283">
+        <v>85.2</v>
+      </c>
+      <c r="H283">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="I283">
+        <v>786</v>
+      </c>
+      <c r="J283">
+        <v>511.05500000000001</v>
+      </c>
+      <c r="K283">
+        <v>0.39</v>
+      </c>
+      <c r="L283">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="M283">
+        <v>53.25</v>
+      </c>
+      <c r="N283">
+        <v>0.61</v>
+      </c>
+      <c r="O283">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="P283">
+        <v>22.3</v>
+      </c>
+      <c r="Q283">
+        <v>2</v>
+      </c>
+      <c r="R283">
+        <v>30</v>
+      </c>
+      <c r="S283">
+        <v>4</v>
+      </c>
+      <c r="T283">
+        <v>211964</v>
+      </c>
+      <c r="U283">
+        <v>212577</v>
+      </c>
+      <c r="V283">
+        <v>613</v>
+      </c>
+      <c r="W283">
+        <v>1</v>
+      </c>
+      <c r="Z283" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="284" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A284">
+        <v>284</v>
+      </c>
+      <c r="B284" t="s">
+        <v>31</v>
+      </c>
+      <c r="C284" t="s">
+        <v>48</v>
+      </c>
+      <c r="D284" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E284" s="2">
+        <v>0.38680555555555557</v>
+      </c>
+      <c r="F284">
+        <v>17.053000000000001</v>
+      </c>
+      <c r="G284">
+        <v>62</v>
+      </c>
+      <c r="H284">
+        <v>5.97</v>
+      </c>
+      <c r="I284">
+        <v>546</v>
+      </c>
+      <c r="J284">
+        <v>354.71699999999998</v>
+      </c>
+      <c r="K284">
+        <v>0.27</v>
+      </c>
+      <c r="L284">
+        <v>7.69</v>
+      </c>
+      <c r="M284">
+        <v>24.84</v>
+      </c>
+      <c r="N284">
+        <v>0.47</v>
+      </c>
+      <c r="O284">
+        <v>6.6</v>
+      </c>
+      <c r="P284">
+        <v>62.08</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>28</v>
+      </c>
+      <c r="R284" t="s">
+        <v>28</v>
+      </c>
+      <c r="S284" t="s">
+        <v>28</v>
+      </c>
+      <c r="T284" t="s">
+        <v>28</v>
+      </c>
+      <c r="U284" t="s">
+        <v>28</v>
+      </c>
+      <c r="V284" t="s">
+        <v>28</v>
+      </c>
+      <c r="W284" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z284" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="285" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A285">
+        <v>285</v>
+      </c>
+      <c r="B285" t="s">
+        <v>31</v>
+      </c>
+      <c r="C285" t="s">
+        <v>36</v>
+      </c>
+      <c r="D285" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E285" s="2">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="F285">
+        <v>17.541</v>
+      </c>
+      <c r="G285">
+        <v>68.2</v>
+      </c>
+      <c r="H285">
+        <v>6.51</v>
+      </c>
+      <c r="I285">
+        <v>556</v>
+      </c>
+      <c r="J285">
+        <v>361.32900000000001</v>
+      </c>
+      <c r="K285">
+        <v>0.27</v>
+      </c>
+      <c r="L285">
+        <v>7.74</v>
+      </c>
+      <c r="M285">
+        <v>35.840000000000003</v>
+      </c>
+      <c r="N285">
+        <v>0.61</v>
+      </c>
+      <c r="O285">
+        <v>9.19</v>
+      </c>
+      <c r="P285">
+        <v>55.85</v>
+      </c>
+      <c r="Q285">
+        <v>4</v>
+      </c>
+      <c r="R285">
+        <v>30</v>
+      </c>
+      <c r="S285">
+        <v>4</v>
+      </c>
+      <c r="T285">
+        <v>212576</v>
+      </c>
+      <c r="U285">
+        <v>213142</v>
+      </c>
+      <c r="V285">
+        <v>566</v>
+      </c>
+      <c r="W285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A286">
+        <v>286</v>
+      </c>
+      <c r="B286" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" t="s">
+        <v>37</v>
+      </c>
+      <c r="D286" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E286" s="2">
+        <v>0.46041666666666664</v>
+      </c>
+      <c r="F286">
+        <v>17.436</v>
+      </c>
+      <c r="G286">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="H286">
+        <v>6.94</v>
+      </c>
+      <c r="I286">
+        <v>597</v>
+      </c>
+      <c r="J286">
+        <v>388.31400000000002</v>
+      </c>
+      <c r="K286">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L286">
+        <v>7.75</v>
+      </c>
+      <c r="M286">
+        <v>25.7</v>
+      </c>
+      <c r="N286">
+        <v>0.54</v>
+      </c>
+      <c r="O286">
+        <v>10.17</v>
+      </c>
+      <c r="P286">
+        <v>54.9</v>
+      </c>
+      <c r="Q286">
+        <v>3.5</v>
+      </c>
+      <c r="R286">
+        <v>30</v>
+      </c>
+      <c r="S286">
+        <v>4</v>
+      </c>
+      <c r="T286">
+        <v>213142</v>
+      </c>
+      <c r="U286">
+        <v>213853</v>
+      </c>
+      <c r="V286">
+        <v>711</v>
+      </c>
+      <c r="W286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A287">
+        <v>287</v>
+      </c>
+      <c r="B287" t="s">
+        <v>31</v>
+      </c>
+      <c r="C287" t="s">
+        <v>38</v>
+      </c>
+      <c r="D287" s="1">
+        <v>46126</v>
+      </c>
+      <c r="E287" s="2">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="F287">
+        <v>17.527000000000001</v>
+      </c>
+      <c r="G287">
+        <v>73</v>
+      </c>
+      <c r="H287">
+        <v>6.96</v>
+      </c>
+      <c r="I287">
+        <v>732</v>
+      </c>
+      <c r="J287">
+        <v>475.74299999999999</v>
+      </c>
+      <c r="K287">
+        <v>0.36</v>
+      </c>
+      <c r="L287">
+        <v>7.93</v>
+      </c>
+      <c r="M287">
+        <v>13.11</v>
+      </c>
+      <c r="N287">
+        <v>0.38</v>
+      </c>
+      <c r="O287">
+        <v>6</v>
+      </c>
+      <c r="P287">
+        <v>56.07</v>
+      </c>
+      <c r="Q287">
+        <v>4.5</v>
+      </c>
+      <c r="R287">
+        <v>30</v>
+      </c>
+      <c r="S287">
+        <v>4</v>
+      </c>
+      <c r="T287">
+        <v>213852</v>
+      </c>
+      <c r="U287">
+        <v>214444</v>
+      </c>
+      <c r="V287">
+        <v>592</v>
+      </c>
+      <c r="W287">
+        <v>1</v>
+      </c>
+      <c r="Z287" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="288" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A288">
+        <v>288</v>
+      </c>
+      <c r="B288" t="s">
+        <v>31</v>
+      </c>
+      <c r="C288" t="s">
+        <v>48</v>
+      </c>
+      <c r="D288" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E288" s="2">
+        <v>0.30763888888888891</v>
+      </c>
+      <c r="F288">
+        <v>16.7</v>
+      </c>
+      <c r="G288">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="H288">
+        <v>7.03</v>
+      </c>
+      <c r="I288">
+        <v>542</v>
+      </c>
+      <c r="J288">
+        <v>352.154</v>
+      </c>
+      <c r="K288">
+        <v>0.26</v>
+      </c>
+      <c r="L288">
+        <v>7.6</v>
+      </c>
+      <c r="M288">
+        <v>22.7</v>
+      </c>
+      <c r="N288">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="O288">
+        <v>35.58</v>
+      </c>
+      <c r="P288">
+        <v>54.31</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>28</v>
+      </c>
+      <c r="R288" t="s">
+        <v>28</v>
+      </c>
+      <c r="S288" t="s">
+        <v>28</v>
+      </c>
+      <c r="T288" t="s">
+        <v>28</v>
+      </c>
+      <c r="U288" t="s">
+        <v>28</v>
+      </c>
+      <c r="V288" t="s">
+        <v>28</v>
+      </c>
+      <c r="W288" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z288" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="289" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>289</v>
+      </c>
+      <c r="B289" t="s">
+        <v>31</v>
+      </c>
+      <c r="C289" t="s">
+        <v>58</v>
+      </c>
+      <c r="D289" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E289" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="F289">
+        <v>14.913</v>
+      </c>
+      <c r="G289">
+        <v>52.6</v>
+      </c>
+      <c r="H289">
+        <v>5.3</v>
+      </c>
+      <c r="I289">
+        <v>1268</v>
+      </c>
+      <c r="J289">
+        <v>824.08399999999995</v>
+      </c>
+      <c r="K289">
+        <v>0.64</v>
+      </c>
+      <c r="L289">
+        <v>7.64</v>
+      </c>
+      <c r="M289">
+        <v>54.92</v>
+      </c>
+      <c r="N289">
+        <v>0.19</v>
+      </c>
+      <c r="O289">
+        <v>3.85</v>
+      </c>
+      <c r="P289">
+        <v>53.22</v>
+      </c>
+      <c r="Q289">
+        <v>1</v>
+      </c>
+      <c r="R289">
+        <v>30</v>
+      </c>
+      <c r="S289">
+        <v>4</v>
+      </c>
+      <c r="T289">
+        <v>214446</v>
+      </c>
+      <c r="U289">
+        <v>215080</v>
+      </c>
+      <c r="V289">
+        <v>634</v>
+      </c>
+      <c r="W289">
+        <v>1</v>
+      </c>
+      <c r="Z289" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="290" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A290">
+        <v>290</v>
+      </c>
+      <c r="B290" t="s">
+        <v>78</v>
+      </c>
+      <c r="C290" t="s">
+        <v>100</v>
+      </c>
+      <c r="D290" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E290" s="2">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="F290">
+        <v>15.569000000000001</v>
+      </c>
+      <c r="G290">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="H290">
+        <v>7.8</v>
+      </c>
+      <c r="I290">
+        <v>430.4</v>
+      </c>
+      <c r="J290">
+        <v>279.75799999999998</v>
+      </c>
+      <c r="K290">
+        <v>0.21</v>
+      </c>
+      <c r="L290">
+        <v>7.76</v>
+      </c>
+      <c r="M290">
+        <v>21.71</v>
+      </c>
+      <c r="N290">
+        <v>0.17</v>
+      </c>
+      <c r="O290">
+        <v>4.08</v>
+      </c>
+      <c r="P290">
+        <v>61.18</v>
+      </c>
+      <c r="Q290">
+        <v>2</v>
+      </c>
+      <c r="R290">
+        <v>30</v>
+      </c>
+      <c r="S290">
+        <v>4</v>
+      </c>
+      <c r="T290">
+        <v>215083</v>
+      </c>
+      <c r="U290">
+        <v>215662</v>
+      </c>
+      <c r="V290">
+        <v>579</v>
+      </c>
+      <c r="W290">
+        <v>1</v>
+      </c>
+      <c r="Z290" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="291" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A291">
+        <v>291</v>
+      </c>
+      <c r="B291" t="s">
+        <v>78</v>
+      </c>
+      <c r="C291" t="s">
+        <v>102</v>
+      </c>
+      <c r="D291" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E291" s="2">
+        <v>0.35208333333333336</v>
+      </c>
+      <c r="F291">
+        <v>16.016999999999999</v>
+      </c>
+      <c r="G291">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="H291">
+        <v>7.59</v>
+      </c>
+      <c r="I291">
+        <v>678</v>
+      </c>
+      <c r="J291">
+        <v>441.01799999999997</v>
+      </c>
+      <c r="K291">
+        <v>0.33</v>
+      </c>
+      <c r="L291">
+        <v>7.93</v>
+      </c>
+      <c r="M291">
+        <v>24.46</v>
+      </c>
+      <c r="N291">
+        <v>0.63</v>
+      </c>
+      <c r="O291">
+        <v>18.34</v>
+      </c>
+      <c r="P291">
+        <v>29.09</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>28</v>
+      </c>
+      <c r="R291" t="s">
+        <v>28</v>
+      </c>
+      <c r="S291" t="s">
+        <v>28</v>
+      </c>
+      <c r="T291" t="s">
+        <v>28</v>
+      </c>
+      <c r="U291" t="s">
+        <v>28</v>
+      </c>
+      <c r="V291" t="s">
+        <v>28</v>
+      </c>
+      <c r="W291" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z291" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="292" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A292">
+        <v>292</v>
+      </c>
+      <c r="B292" t="s">
+        <v>31</v>
+      </c>
+      <c r="C292" t="s">
+        <v>35</v>
+      </c>
+      <c r="D292" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E292" s="2">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F292">
+        <v>15.96</v>
+      </c>
+      <c r="G292">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="H292">
+        <v>7.83</v>
+      </c>
+      <c r="I292">
+        <v>792</v>
+      </c>
+      <c r="J292">
+        <v>514.90800000000002</v>
+      </c>
+      <c r="K292">
+        <v>0.39</v>
+      </c>
+      <c r="L292">
+        <v>7.8</v>
+      </c>
+      <c r="M292">
+        <v>29.69</v>
+      </c>
+      <c r="N292">
+        <v>0.52</v>
+      </c>
+      <c r="O292">
+        <v>13.89</v>
+      </c>
+      <c r="P292">
+        <v>50.44</v>
+      </c>
+      <c r="Q292">
+        <v>2.5</v>
+      </c>
+      <c r="R292">
+        <v>30</v>
+      </c>
+      <c r="S292">
+        <v>4</v>
+      </c>
+      <c r="T292">
+        <v>215655</v>
+      </c>
+      <c r="U292">
+        <v>216203</v>
+      </c>
+      <c r="V292">
+        <v>548</v>
+      </c>
+      <c r="W292">
+        <v>1</v>
+      </c>
+      <c r="Z292" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="293" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A293">
+        <v>293</v>
+      </c>
+      <c r="B293" t="s">
+        <v>31</v>
+      </c>
+      <c r="C293" t="s">
+        <v>32</v>
+      </c>
+      <c r="D293" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E293" s="2">
+        <v>0.39097222222222222</v>
+      </c>
+      <c r="F293">
+        <v>16.7</v>
+      </c>
+      <c r="G293">
+        <v>97</v>
+      </c>
+      <c r="H293">
+        <v>9.43</v>
+      </c>
+      <c r="I293">
+        <v>179.1</v>
+      </c>
+      <c r="J293">
+        <v>116.39100000000001</v>
+      </c>
+      <c r="K293">
+        <v>0.08</v>
+      </c>
+      <c r="L293">
+        <v>7.82</v>
+      </c>
+      <c r="M293">
+        <v>11.96</v>
+      </c>
+      <c r="N293">
+        <v>0.15</v>
+      </c>
+      <c r="O293">
+        <v>2.02</v>
+      </c>
+      <c r="P293">
+        <v>10.27</v>
+      </c>
+      <c r="Q293">
+        <v>1</v>
+      </c>
+      <c r="R293">
+        <v>30</v>
+      </c>
+      <c r="S293">
+        <v>4</v>
+      </c>
+      <c r="T293">
+        <v>216199</v>
+      </c>
+      <c r="U293">
+        <v>216726</v>
+      </c>
+      <c r="V293">
+        <v>527</v>
+      </c>
+      <c r="W293">
+        <v>1</v>
+      </c>
+      <c r="Z293" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="294" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A294">
+        <v>294</v>
+      </c>
+      <c r="B294" t="s">
+        <v>31</v>
+      </c>
+      <c r="C294" t="s">
+        <v>34</v>
+      </c>
+      <c r="D294" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E294" s="2">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="F294">
+        <v>18.074999999999999</v>
+      </c>
+      <c r="G294">
+        <v>88.4</v>
+      </c>
+      <c r="H294">
+        <v>8.34</v>
+      </c>
+      <c r="I294">
+        <v>719</v>
+      </c>
+      <c r="J294">
+        <v>467.21800000000002</v>
+      </c>
+      <c r="K294">
+        <v>0.35</v>
+      </c>
+      <c r="L294">
+        <v>8.08</v>
+      </c>
+      <c r="M294">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="N294">
+        <v>1.42</v>
+      </c>
+      <c r="O294">
+        <v>3.45</v>
+      </c>
+      <c r="P294">
+        <v>25.89</v>
+      </c>
+      <c r="Q294">
+        <v>4</v>
+      </c>
+      <c r="R294">
+        <v>30</v>
+      </c>
+      <c r="S294">
+        <v>4</v>
+      </c>
+      <c r="T294">
+        <v>216727</v>
+      </c>
+      <c r="U294">
+        <v>217280</v>
+      </c>
+      <c r="V294">
+        <v>553</v>
+      </c>
+      <c r="W294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A295">
+        <v>295</v>
+      </c>
+      <c r="B295" t="s">
+        <v>31</v>
+      </c>
+      <c r="C295" t="s">
+        <v>36</v>
+      </c>
+      <c r="D295" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E295" s="2">
+        <v>0.45694444444444443</v>
+      </c>
+      <c r="F295">
+        <v>17.573</v>
+      </c>
+      <c r="G295">
+        <v>74</v>
+      </c>
+      <c r="H295">
+        <v>7.05</v>
+      </c>
+      <c r="I295">
+        <v>578</v>
+      </c>
+      <c r="J295">
+        <v>375.44299999999998</v>
+      </c>
+      <c r="K295">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L295">
+        <v>7.89</v>
+      </c>
+      <c r="M295">
+        <v>26.86</v>
+      </c>
+      <c r="N295">
+        <v>1.71</v>
+      </c>
+      <c r="O295">
+        <v>29.53</v>
+      </c>
+      <c r="P295">
+        <v>54.88</v>
+      </c>
+      <c r="Q295">
+        <v>4.5</v>
+      </c>
+      <c r="R295">
+        <v>30</v>
+      </c>
+      <c r="S295">
+        <v>4</v>
+      </c>
+      <c r="T295">
+        <v>217284</v>
+      </c>
+      <c r="U295">
+        <v>217906</v>
+      </c>
+      <c r="V295">
+        <v>622</v>
+      </c>
+      <c r="W295">
+        <v>1</v>
+      </c>
+      <c r="Z295" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="296" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A296">
+        <v>296</v>
+      </c>
+      <c r="B296" t="s">
+        <v>31</v>
+      </c>
+      <c r="C296" t="s">
+        <v>37</v>
+      </c>
+      <c r="D296" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E296" s="2">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="F296">
+        <v>17.673999999999999</v>
+      </c>
+      <c r="G296">
+        <v>63.7</v>
+      </c>
+      <c r="H296">
+        <v>6.06</v>
+      </c>
+      <c r="I296">
+        <v>551</v>
+      </c>
+      <c r="J296">
+        <v>357.96600000000001</v>
+      </c>
+      <c r="K296">
+        <v>0.27</v>
+      </c>
+      <c r="L296">
+        <v>7.76</v>
+      </c>
+      <c r="M296">
+        <v>23.83</v>
+      </c>
+      <c r="N296">
+        <v>0.33</v>
+      </c>
+      <c r="O296">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="P296">
+        <v>42.34</v>
+      </c>
+      <c r="Q296">
+        <v>3</v>
+      </c>
+      <c r="R296">
+        <v>30</v>
+      </c>
+      <c r="S296">
+        <v>4</v>
+      </c>
+      <c r="T296">
+        <v>217921</v>
+      </c>
+      <c r="U296">
+        <v>218580</v>
+      </c>
+      <c r="V296">
+        <v>659</v>
+      </c>
+      <c r="W296">
+        <v>1</v>
+      </c>
+      <c r="Z296" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="297" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A297">
+        <v>297</v>
+      </c>
+      <c r="B297" t="s">
+        <v>31</v>
+      </c>
+      <c r="C297" t="s">
+        <v>38</v>
+      </c>
+      <c r="D297" s="1">
+        <v>46133</v>
+      </c>
+      <c r="E297" s="2">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="F297">
+        <v>18.021999999999998</v>
+      </c>
+      <c r="G297">
+        <v>69.5</v>
+      </c>
+      <c r="H297">
+        <v>6.57</v>
+      </c>
+      <c r="I297">
+        <v>533</v>
+      </c>
+      <c r="J297">
+        <v>346.28199999999998</v>
+      </c>
+      <c r="K297">
+        <v>0.26</v>
+      </c>
+      <c r="L297">
+        <v>7.83</v>
+      </c>
+      <c r="M297">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="N297">
+        <v>0.09</v>
+      </c>
+      <c r="O297">
+        <v>2.19</v>
+      </c>
+      <c r="P297">
+        <v>52.36</v>
+      </c>
+      <c r="Q297">
+        <v>1.5</v>
+      </c>
+      <c r="R297">
+        <v>30</v>
+      </c>
+      <c r="S297">
+        <v>4</v>
+      </c>
+      <c r="T297">
+        <v>218575</v>
+      </c>
+      <c r="U297">
+        <v>219213</v>
+      </c>
+      <c r="V297">
+        <v>638</v>
+      </c>
+      <c r="W297">
+        <v>1</v>
+      </c>
+      <c r="Z297" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="298" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A298">
+        <v>298</v>
+      </c>
+      <c r="B298" t="s">
+        <v>31</v>
+      </c>
+      <c r="C298" t="s">
+        <v>48</v>
+      </c>
+      <c r="D298" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E298" s="2">
+        <v>0.30069444444444443</v>
+      </c>
+      <c r="F298">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="G298">
+        <v>58.4</v>
+      </c>
+      <c r="H298">
+        <v>5.57</v>
+      </c>
+      <c r="I298">
+        <v>480.6</v>
+      </c>
+      <c r="J298">
+        <v>312.37299999999999</v>
+      </c>
+      <c r="K298">
+        <v>0.23</v>
+      </c>
+      <c r="L298">
+        <v>7.45</v>
+      </c>
+      <c r="M298">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="N298">
+        <v>0.44</v>
+      </c>
+      <c r="O298">
+        <v>11.94</v>
+      </c>
+      <c r="P298">
+        <v>50.74</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>28</v>
+      </c>
+      <c r="R298" t="s">
+        <v>28</v>
+      </c>
+      <c r="S298" t="s">
+        <v>28</v>
+      </c>
+      <c r="T298" t="s">
+        <v>28</v>
+      </c>
+      <c r="U298" t="s">
+        <v>28</v>
+      </c>
+      <c r="V298" t="s">
+        <v>28</v>
+      </c>
+      <c r="W298" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z298" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="299" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A299">
+        <v>299</v>
+      </c>
+      <c r="B299" t="s">
+        <v>31</v>
+      </c>
+      <c r="C299" t="s">
+        <v>35</v>
+      </c>
+      <c r="D299" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E299" s="2">
+        <v>0.32361111111111113</v>
+      </c>
+      <c r="F299">
+        <v>17.222000000000001</v>
+      </c>
+      <c r="G299">
+        <v>67</v>
+      </c>
+      <c r="H299">
+        <v>6.43</v>
+      </c>
+      <c r="I299">
+        <v>562</v>
+      </c>
+      <c r="J299">
+        <v>365.59500000000003</v>
+      </c>
+      <c r="K299">
+        <v>0.27</v>
+      </c>
+      <c r="L299">
+        <v>7.51</v>
+      </c>
+      <c r="M299">
+        <v>24.74</v>
+      </c>
+      <c r="N299">
+        <v>0.52</v>
+      </c>
+      <c r="O299">
+        <v>16.59</v>
+      </c>
+      <c r="P299">
+        <v>43.46</v>
+      </c>
+      <c r="Q299">
+        <v>4</v>
+      </c>
+      <c r="R299">
+        <v>30</v>
+      </c>
+      <c r="S299">
+        <v>4</v>
+      </c>
+      <c r="T299">
+        <v>219219</v>
+      </c>
+      <c r="U299">
+        <v>219669</v>
+      </c>
+      <c r="V299">
+        <v>450</v>
+      </c>
+      <c r="W299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A300">
+        <v>300</v>
+      </c>
+      <c r="B300" t="s">
+        <v>31</v>
+      </c>
+      <c r="C300" t="s">
+        <v>32</v>
+      </c>
+      <c r="D300" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E300" s="2">
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="F300">
+        <v>17.265999999999998</v>
+      </c>
+      <c r="G300">
+        <v>92.9</v>
+      </c>
+      <c r="H300">
+        <v>8.93</v>
+      </c>
+      <c r="I300">
+        <v>186.2</v>
+      </c>
+      <c r="J300">
+        <v>121.033</v>
+      </c>
+      <c r="K300">
+        <v>0.09</v>
+      </c>
+      <c r="L300">
+        <v>7.78</v>
+      </c>
+      <c r="M300">
+        <v>18</v>
+      </c>
+      <c r="N300">
+        <v>0.16</v>
+      </c>
+      <c r="O300">
+        <v>2.54</v>
+      </c>
+      <c r="P300">
+        <v>17.14</v>
+      </c>
+      <c r="Q300">
+        <v>1</v>
+      </c>
+      <c r="R300">
+        <v>30</v>
+      </c>
+      <c r="S300">
+        <v>4</v>
+      </c>
+      <c r="T300">
+        <v>219669</v>
+      </c>
+      <c r="U300">
+        <v>220336</v>
+      </c>
+      <c r="V300">
+        <v>667</v>
+      </c>
+      <c r="W300">
+        <v>1</v>
+      </c>
+      <c r="Z300" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="301" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A301">
+        <v>301</v>
+      </c>
+      <c r="B301" t="s">
+        <v>31</v>
+      </c>
+      <c r="C301" t="s">
+        <v>34</v>
+      </c>
+      <c r="D301" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E301" s="2">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="F301">
+        <v>17.608000000000001</v>
+      </c>
+      <c r="G301">
+        <v>87.5</v>
+      </c>
+      <c r="H301">
+        <v>8.35</v>
+      </c>
+      <c r="I301">
+        <v>201.5</v>
+      </c>
+      <c r="J301">
+        <v>130.96100000000001</v>
+      </c>
+      <c r="K301">
+        <v>0.1</v>
+      </c>
+      <c r="L301">
+        <v>7.57</v>
+      </c>
+      <c r="M301">
+        <v>8.74</v>
+      </c>
+      <c r="N301">
+        <v>0.17</v>
+      </c>
+      <c r="O301">
+        <v>6.31</v>
+      </c>
+      <c r="P301">
+        <v>28.4</v>
+      </c>
+      <c r="Q301">
+        <v>3</v>
+      </c>
+      <c r="R301">
+        <v>30</v>
+      </c>
+      <c r="S301">
+        <v>4</v>
+      </c>
+      <c r="T301">
+        <v>220334</v>
+      </c>
+      <c r="U301">
+        <v>220847</v>
+      </c>
+      <c r="V301">
+        <v>513</v>
+      </c>
+      <c r="W301">
+        <v>1</v>
+      </c>
+      <c r="Z301" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="302" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A302">
+        <v>302</v>
+      </c>
+      <c r="B302" t="s">
+        <v>31</v>
+      </c>
+      <c r="C302" t="s">
+        <v>36</v>
+      </c>
+      <c r="D302" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E302" s="2">
+        <v>0.42430555555555555</v>
+      </c>
+      <c r="F302">
+        <v>20.173999999999999</v>
+      </c>
+      <c r="G302">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="H302">
+        <v>5.84</v>
+      </c>
+      <c r="I302">
+        <v>583</v>
+      </c>
+      <c r="J302">
+        <v>379.10500000000002</v>
+      </c>
+      <c r="K302">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L302">
+        <v>7.58</v>
+      </c>
+      <c r="M302">
+        <v>28.04</v>
+      </c>
+      <c r="N302">
+        <v>0.19</v>
+      </c>
+      <c r="O302">
+        <v>6.22</v>
+      </c>
+      <c r="P302">
+        <v>40.06</v>
+      </c>
+      <c r="Q302">
+        <v>2.5</v>
+      </c>
+      <c r="R302">
+        <v>30</v>
+      </c>
+      <c r="S302">
+        <v>4</v>
+      </c>
+      <c r="T302">
+        <v>220846</v>
+      </c>
+      <c r="U302">
+        <v>221458</v>
+      </c>
+      <c r="V302">
+        <v>612</v>
+      </c>
+      <c r="W302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A303">
+        <v>303</v>
+      </c>
+      <c r="B303" t="s">
+        <v>31</v>
+      </c>
+      <c r="C303" t="s">
+        <v>37</v>
+      </c>
+      <c r="D303" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E303" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F303">
+        <v>18.350999999999999</v>
+      </c>
+      <c r="G303">
+        <v>71.8</v>
+      </c>
+      <c r="H303">
+        <v>6.74</v>
+      </c>
+      <c r="I303">
+        <v>530</v>
+      </c>
+      <c r="J303">
+        <v>344.82299999999998</v>
+      </c>
+      <c r="K303">
+        <v>0.26</v>
+      </c>
+      <c r="L303">
+        <v>7.69</v>
+      </c>
+      <c r="M303">
+        <v>28.17</v>
+      </c>
+      <c r="N303">
+        <v>0.31</v>
+      </c>
+      <c r="O303">
+        <v>9.81</v>
+      </c>
+      <c r="P303">
+        <v>41.34</v>
+      </c>
+      <c r="Q303">
+        <v>3</v>
+      </c>
+      <c r="R303">
+        <v>30</v>
+      </c>
+      <c r="S303">
+        <v>4</v>
+      </c>
+      <c r="T303">
+        <v>221466</v>
+      </c>
+      <c r="U303">
+        <v>222011</v>
+      </c>
+      <c r="V303">
+        <v>545</v>
+      </c>
+      <c r="W303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A304">
+        <v>304</v>
+      </c>
+      <c r="B304" t="s">
+        <v>31</v>
+      </c>
+      <c r="C304" t="s">
+        <v>38</v>
+      </c>
+      <c r="D304" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E304" s="2">
+        <v>0.46597222222222223</v>
+      </c>
+      <c r="F304">
+        <v>18.38</v>
+      </c>
+      <c r="G304">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="H304">
+        <v>6.44</v>
+      </c>
+      <c r="I304">
+        <v>516</v>
+      </c>
+      <c r="J304">
+        <v>335.608</v>
+      </c>
+      <c r="K304">
+        <v>0.25</v>
+      </c>
+      <c r="L304">
+        <v>7.67</v>
+      </c>
+      <c r="M304">
+        <v>22.7</v>
+      </c>
+      <c r="N304">
+        <v>0.09</v>
+      </c>
+      <c r="O304">
+        <v>2.34</v>
+      </c>
+      <c r="P304">
+        <v>41.94</v>
+      </c>
+      <c r="Q304">
+        <v>2</v>
+      </c>
+      <c r="R304">
+        <v>30</v>
+      </c>
+      <c r="S304">
+        <v>4</v>
+      </c>
+      <c r="T304">
+        <v>222013</v>
+      </c>
+      <c r="U304">
+        <v>222647</v>
+      </c>
+      <c r="V304">
+        <v>634</v>
+      </c>
+      <c r="W304">
+        <v>1</v>
+      </c>
+      <c r="Z304" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A305">
+        <v>305</v>
+      </c>
+      <c r="B305" t="s">
+        <v>78</v>
+      </c>
+      <c r="C305" t="s">
+        <v>113</v>
+      </c>
+      <c r="D305" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E305" s="2">
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="F305">
+        <v>17.606000000000002</v>
+      </c>
+      <c r="G305">
+        <v>88.2</v>
+      </c>
+      <c r="H305">
+        <v>8.4</v>
+      </c>
+      <c r="I305">
+        <v>460.3</v>
+      </c>
+      <c r="J305">
+        <v>299.17099999999999</v>
+      </c>
+      <c r="K305">
+        <v>0.22</v>
+      </c>
+      <c r="L305">
+        <v>7.62</v>
+      </c>
+      <c r="M305">
+        <v>20.46</v>
+      </c>
+      <c r="N305">
+        <v>0.36</v>
+      </c>
+      <c r="O305">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="P305">
+        <v>44.87</v>
+      </c>
+      <c r="Q305" t="s">
+        <v>28</v>
+      </c>
+      <c r="R305" t="s">
+        <v>28</v>
+      </c>
+      <c r="S305" t="s">
+        <v>28</v>
+      </c>
+      <c r="T305" t="s">
+        <v>28</v>
+      </c>
+      <c r="U305" t="s">
+        <v>28</v>
+      </c>
+      <c r="V305" t="s">
+        <v>28</v>
+      </c>
+      <c r="W305" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A306">
+        <v>306</v>
+      </c>
+      <c r="B306" t="s">
+        <v>78</v>
+      </c>
+      <c r="C306" t="s">
+        <v>114</v>
+      </c>
+      <c r="D306" s="1">
+        <v>46140</v>
+      </c>
+      <c r="E306" s="2">
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="F306">
+        <v>17.434000000000001</v>
+      </c>
+      <c r="G306">
+        <v>86.8</v>
+      </c>
+      <c r="H306">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="I306">
+        <v>555</v>
+      </c>
+      <c r="J306">
+        <v>360.59500000000003</v>
+      </c>
+      <c r="K306">
+        <v>0.27</v>
+      </c>
+      <c r="L306">
+        <v>7.67</v>
+      </c>
+      <c r="M306">
+        <v>20.65</v>
+      </c>
+      <c r="N306">
+        <v>0.48</v>
+      </c>
+      <c r="O306">
+        <v>14.04</v>
+      </c>
+      <c r="P306">
+        <v>49.67</v>
+      </c>
+      <c r="Q306" t="s">
+        <v>28</v>
+      </c>
+      <c r="R306" t="s">
+        <v>28</v>
+      </c>
+      <c r="S306" t="s">
+        <v>28</v>
+      </c>
+      <c r="T306" t="s">
+        <v>28</v>
+      </c>
+      <c r="U306" t="s">
+        <v>28</v>
+      </c>
+      <c r="V306" t="s">
+        <v>28</v>
+      </c>
+      <c r="W306" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
